--- a/Data/National Accounts/PSA-17FIA_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-17FIA_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B474BF4-18C9-4016-BE05-951ECF5050B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E883F87-82CF-4DDD-94D9-298E0C981317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="FIA" sheetId="17" r:id="rId1"/>
@@ -692,10 +692,10 @@
     <t>Table 18.7 Gross Value Added in Financial and Insurance Activities, by Industry</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -743,10 +743,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1208,7 +1210,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1218,7 +1220,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -2007,19 +2009,19 @@
         <v>391049.66500519175</v>
       </c>
       <c r="CW12" s="19">
-        <v>362255.94604121963</v>
+        <v>360862.88108547061</v>
       </c>
       <c r="CX12" s="19">
-        <v>483635.14417858224</v>
+        <v>483549.39403888211</v>
       </c>
       <c r="CY12" s="19">
-        <v>367304.66761291411</v>
+        <v>368114.1411166382</v>
       </c>
       <c r="CZ12" s="19">
-        <v>413399.22408448666</v>
+        <v>413339.43127555435</v>
       </c>
       <c r="DA12" s="19">
-        <v>384820.03544534219</v>
+        <v>385303.36760576011</v>
       </c>
       <c r="DB12" s="10"/>
       <c r="DC12" s="10"/>
@@ -2395,22 +2397,22 @@
         <v>242973.97616764033</v>
       </c>
       <c r="CV13" s="19">
-        <v>186576.95161608633</v>
+        <v>185941.08104794048</v>
       </c>
       <c r="CW13" s="19">
-        <v>243570.86094178318</v>
+        <v>244658.4134290822</v>
       </c>
       <c r="CX13" s="19">
-        <v>188431.86756203652</v>
+        <v>188488.15133652484</v>
       </c>
       <c r="CY13" s="19">
-        <v>259545.39944401954</v>
+        <v>259385.18990449107</v>
       </c>
       <c r="CZ13" s="19">
-        <v>196698.59587551426</v>
+        <v>196203.0783505351</v>
       </c>
       <c r="DA13" s="19">
-        <v>256102.59957905335</v>
+        <v>254405.15202279875</v>
       </c>
       <c r="DB13" s="10"/>
       <c r="DC13" s="10"/>
@@ -2786,22 +2788,22 @@
         <v>77622.661439921125</v>
       </c>
       <c r="CV14" s="19">
-        <v>81702.166942802578</v>
+        <v>81946.466226194549</v>
       </c>
       <c r="CW14" s="19">
         <v>96659.135263414457</v>
       </c>
       <c r="CX14" s="19">
-        <v>93487.915714654417</v>
+        <v>93476.312489711723</v>
       </c>
       <c r="CY14" s="19">
-        <v>86504.511726402023</v>
+        <v>86293.180685475003</v>
       </c>
       <c r="CZ14" s="19">
-        <v>91219.165763467128</v>
+        <v>91670.874603439457</v>
       </c>
       <c r="DA14" s="19">
-        <v>109347.32126632318</v>
+        <v>110154.99172421533</v>
       </c>
       <c r="DB14" s="10"/>
       <c r="DC14" s="10"/>
@@ -3177,22 +3179,22 @@
         <v>40359.630011840367</v>
       </c>
       <c r="CV15" s="19">
-        <v>33816.517383106911</v>
+        <v>33911.414916153029</v>
       </c>
       <c r="CW15" s="19">
-        <v>41979.682921837324</v>
+        <v>42764.488037322255</v>
       </c>
       <c r="CX15" s="19">
-        <v>39345.424388646672</v>
+        <v>39333.310416632507</v>
       </c>
       <c r="CY15" s="19">
-        <v>48001.590322028613</v>
+        <v>47985.8575788827</v>
       </c>
       <c r="CZ15" s="19">
-        <v>39133.445150656044</v>
+        <v>39223.906797147829</v>
       </c>
       <c r="DA15" s="19">
-        <v>48492.691240964996</v>
+        <v>49494.969388841491</v>
       </c>
       <c r="DB15" s="10"/>
       <c r="DC15" s="10"/>
@@ -3748,22 +3750,22 @@
         <v>713299.75493119692</v>
       </c>
       <c r="CV17" s="20">
-        <v>693145.30094718758</v>
+        <v>692848.62719547981</v>
       </c>
       <c r="CW17" s="20">
-        <v>744465.6251682546</v>
+        <v>744944.91781528958</v>
       </c>
       <c r="CX17" s="20">
-        <v>804900.35184391984</v>
+        <v>804847.16828175122</v>
       </c>
       <c r="CY17" s="20">
-        <v>761356.16910536424</v>
+        <v>761778.36928548699</v>
       </c>
       <c r="CZ17" s="20">
-        <v>740450.43087412405</v>
+        <v>740437.29102667677</v>
       </c>
       <c r="DA17" s="20">
-        <v>798762.64753168379</v>
+        <v>799358.48074161576</v>
       </c>
       <c r="DB17" s="10"/>
       <c r="DC17" s="10"/>
@@ -4324,7 +4326,7 @@
     </row>
     <row r="24" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:179" x14ac:dyDescent="0.2">
@@ -4334,7 +4336,7 @@
     </row>
     <row r="27" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
@@ -5123,19 +5125,19 @@
         <v>321805.66915094905</v>
       </c>
       <c r="CW33" s="19">
-        <v>293302.25083285681</v>
+        <v>292174.34916128259</v>
       </c>
       <c r="CX33" s="19">
-        <v>383760.14419142884</v>
+        <v>383720.54987272876</v>
       </c>
       <c r="CY33" s="19">
-        <v>290204.7974425737</v>
+        <v>290870.59760381113</v>
       </c>
       <c r="CZ33" s="19">
-        <v>335679.70289662661</v>
+        <v>335684.27783661347</v>
       </c>
       <c r="DA33" s="19">
-        <v>306516.43539141957</v>
+        <v>306949.24128408189</v>
       </c>
       <c r="DB33" s="10"/>
       <c r="DC33" s="10"/>
@@ -5511,22 +5513,22 @@
         <v>197077.13496332135</v>
       </c>
       <c r="CV34" s="19">
-        <v>155719.01404404742</v>
+        <v>155188.31002581987</v>
       </c>
       <c r="CW34" s="19">
-        <v>198833.74494715154</v>
+        <v>199721.54463320645</v>
       </c>
       <c r="CX34" s="19">
-        <v>151408.90151675628</v>
+        <v>151467.5401597193</v>
       </c>
       <c r="CY34" s="19">
-        <v>207873.20355137379</v>
+        <v>207771.74357305057</v>
       </c>
       <c r="CZ34" s="19">
-        <v>162026.41047320096</v>
+        <v>161648.52175617364</v>
       </c>
       <c r="DA34" s="19">
-        <v>205697.92759586097</v>
+        <v>204370.73525530164</v>
       </c>
       <c r="DB34" s="10"/>
       <c r="DC34" s="10"/>
@@ -5902,7 +5904,7 @@
         <v>64497.174203178147</v>
       </c>
       <c r="CV35" s="19">
-        <v>68922.345398903271</v>
+        <v>69128.43148230463</v>
       </c>
       <c r="CW35" s="19">
         <v>79856.716755934816</v>
@@ -5911,13 +5913,13 @@
         <v>73109.383381391948</v>
       </c>
       <c r="CY35" s="19">
-        <v>70983.365274625685</v>
+        <v>70821.571386357173</v>
       </c>
       <c r="CZ35" s="19">
-        <v>75965.768674651728</v>
+        <v>76362.47066504159</v>
       </c>
       <c r="DA35" s="19">
-        <v>88884.8644838537</v>
+        <v>89564.310177072039</v>
       </c>
       <c r="DB35" s="10"/>
       <c r="DC35" s="10"/>
@@ -6293,10 +6295,10 @@
         <v>31672.61610750838</v>
       </c>
       <c r="CV36" s="19">
-        <v>27732.412195209676</v>
+        <v>27810.236220461244</v>
       </c>
       <c r="CW36" s="19">
-        <v>33779.292157946096</v>
+        <v>34410.791955893023</v>
       </c>
       <c r="CX36" s="19">
         <v>31149.32869481633</v>
@@ -6305,10 +6307,10 @@
         <v>37278.603683510853</v>
       </c>
       <c r="CZ36" s="19">
-        <v>31731.967483638495</v>
+        <v>31826.137865384168</v>
       </c>
       <c r="DA36" s="19">
-        <v>38406.05305841651</v>
+        <v>39222.889094905258</v>
       </c>
       <c r="DB36" s="10"/>
       <c r="DC36" s="10"/>
@@ -6864,22 +6866,22 @@
         <v>575273.56153178355</v>
       </c>
       <c r="CV38" s="20">
-        <v>574179.44078910933</v>
+        <v>573932.6468795347</v>
       </c>
       <c r="CW38" s="20">
-        <v>605772.00469388929</v>
+        <v>606163.4025063169</v>
       </c>
       <c r="CX38" s="20">
-        <v>639427.75778439338</v>
+        <v>639446.80210865638</v>
       </c>
       <c r="CY38" s="20">
-        <v>606339.96995208412</v>
+        <v>606742.51624672976</v>
       </c>
       <c r="CZ38" s="20">
-        <v>605403.8495281178</v>
+        <v>605521.40812321287</v>
       </c>
       <c r="DA38" s="20">
-        <v>639505.28052955074</v>
+        <v>640107.17581136082</v>
       </c>
       <c r="DB38" s="10"/>
       <c r="DC38" s="10"/>
@@ -7448,7 +7450,7 @@
     </row>
     <row r="45" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CX45" s="6"/>
       <c r="CY45" s="6"/>
@@ -7478,7 +7480,7 @@
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="CT48" s="8"/>
       <c r="CU48" s="8"/>
@@ -8266,19 +8268,19 @@
         <v>12.005405323221723</v>
       </c>
       <c r="CS54" s="15">
-        <v>9.4447791053603254</v>
+        <v>9.0239062721397403</v>
       </c>
       <c r="CT54" s="15">
-        <v>7.2678268619556121</v>
+        <v>7.248807915029488</v>
       </c>
       <c r="CU54" s="15">
-        <v>4.2461918099481011</v>
+        <v>4.4759316896036125</v>
       </c>
       <c r="CV54" s="15">
-        <v>5.7152738077395355</v>
+        <v>5.6999834714259805</v>
       </c>
       <c r="CW54" s="15">
-        <v>6.2287699210201737</v>
+        <v>6.7727903869671593</v>
       </c>
       <c r="CX54" s="17"/>
       <c r="CY54" s="17"/>
@@ -8642,22 +8644,22 @@
         <v>8.2727116889317074</v>
       </c>
       <c r="CR55" s="15">
-        <v>14.254069341422507</v>
+        <v>13.864681481047342</v>
       </c>
       <c r="CS55" s="15">
-        <v>13.385260216628254</v>
+        <v>13.891529403733969</v>
       </c>
       <c r="CT55" s="15">
-        <v>11.27751776992163</v>
+        <v>11.310755877662189</v>
       </c>
       <c r="CU55" s="15">
-        <v>6.8202461587679295</v>
+        <v>6.7543092456649845</v>
       </c>
       <c r="CV55" s="15">
-        <v>5.4249167283292934</v>
+        <v>5.5189510810409956</v>
       </c>
       <c r="CW55" s="15">
-        <v>5.145007325102597</v>
+        <v>3.983815008488051</v>
       </c>
       <c r="CX55" s="17"/>
       <c r="CY55" s="17"/>
@@ -9021,22 +9023,22 @@
         <v>13.847818813772378</v>
       </c>
       <c r="CR56" s="15">
-        <v>8.741717287411106</v>
+        <v>9.0668680710705587</v>
       </c>
       <c r="CS56" s="15">
         <v>10.531733670285618</v>
       </c>
       <c r="CT56" s="15">
-        <v>14.697674389772658</v>
+        <v>14.683438721920012</v>
       </c>
       <c r="CU56" s="15">
-        <v>11.442341864759854</v>
+        <v>11.170087555249239</v>
       </c>
       <c r="CV56" s="15">
-        <v>11.648404414202545</v>
+        <v>11.866781845605033</v>
       </c>
       <c r="CW56" s="15">
-        <v>13.126732375921861</v>
+        <v>13.962318640676969</v>
       </c>
       <c r="CX56" s="17"/>
       <c r="CY56" s="17"/>
@@ -9400,22 +9402,22 @@
         <v>17.66713080085907</v>
       </c>
       <c r="CR57" s="15">
-        <v>16.614617126247239</v>
+        <v>16.941866658096629</v>
       </c>
       <c r="CS57" s="15">
-        <v>16.65713732835772</v>
+        <v>18.838028458564395</v>
       </c>
       <c r="CT57" s="15">
-        <v>13.519226941699628</v>
+        <v>13.484275768606196</v>
       </c>
       <c r="CU57" s="15">
-        <v>18.934663940046818</v>
+        <v>18.895682554089348</v>
       </c>
       <c r="CV57" s="15">
-        <v>15.722872072584295</v>
+        <v>15.665792459943333</v>
       </c>
       <c r="CW57" s="15">
-        <v>15.514667729278358</v>
+        <v>15.738482232373002</v>
       </c>
       <c r="CX57" s="17"/>
       <c r="CY57" s="17"/>
@@ -9955,22 +9957,22 @@
         <v>12.555635247641177</v>
       </c>
       <c r="CR59" s="15">
-        <v>12.420044284729272</v>
+        <v>12.37192727916127</v>
       </c>
       <c r="CS59" s="15">
-        <v>11.239449855949474</v>
+        <v>11.311066662117142</v>
       </c>
       <c r="CT59" s="15">
-        <v>9.3065387047919899</v>
+        <v>9.2993163062884605</v>
       </c>
       <c r="CU59" s="15">
-        <v>6.7371976286186595</v>
+        <v>6.7963873559673686</v>
       </c>
       <c r="CV59" s="15">
-        <v>6.8247061420302089</v>
+        <v>6.8685513636401083</v>
       </c>
       <c r="CW59" s="15">
-        <v>7.2934223593141354</v>
+        <v>7.3043740047124004</v>
       </c>
       <c r="CX59" s="17"/>
       <c r="CY59" s="17"/>
@@ -10535,7 +10537,7 @@
     </row>
     <row r="66" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CX66" s="6"/>
       <c r="CY66" s="6"/>
@@ -10559,7 +10561,7 @@
     </row>
     <row r="69" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="CX69" s="6"/>
       <c r="CY69" s="6"/>
@@ -11344,19 +11346,19 @@
         <v>8.7231367148200292</v>
       </c>
       <c r="CS75" s="15">
-        <v>6.5438185514050673</v>
+        <v>6.134101439794776</v>
       </c>
       <c r="CT75" s="15">
-        <v>4.8665972537527153</v>
+        <v>4.8557776792463443</v>
       </c>
       <c r="CU75" s="15">
-        <v>2.8997832592391006</v>
+        <v>3.1358603085816554</v>
       </c>
       <c r="CV75" s="15">
-        <v>4.3113080581466363</v>
+        <v>4.3127297049432798</v>
       </c>
       <c r="CW75" s="15">
-        <v>4.5053130417649072</v>
+        <v>5.0568751723798471</v>
       </c>
       <c r="CX75" s="17"/>
       <c r="CY75" s="17"/>
@@ -11720,22 +11722,22 @@
         <v>3.9352812815154294</v>
       </c>
       <c r="CR76" s="15">
-        <v>10.924081522510235</v>
+        <v>10.546042551845119</v>
       </c>
       <c r="CS76" s="15">
-        <v>10.3787161292382</v>
+        <v>10.87156099092266</v>
       </c>
       <c r="CT76" s="15">
-        <v>8.8082271874857128</v>
+        <v>8.8503671589244419</v>
       </c>
       <c r="CU76" s="15">
-        <v>5.478092925423212</v>
+        <v>5.4266105561761862</v>
       </c>
       <c r="CV76" s="15">
-        <v>4.0504985649147471</v>
+        <v>4.1628211102233905</v>
       </c>
       <c r="CW76" s="15">
-        <v>3.4522221821722781</v>
+        <v>2.3278363036063752</v>
       </c>
       <c r="CX76" s="17"/>
       <c r="CY76" s="17"/>
@@ -12099,7 +12101,7 @@
         <v>9.1870492846512661</v>
       </c>
       <c r="CR77" s="15">
-        <v>5.5032896649294969</v>
+        <v>5.8187571613874951</v>
       </c>
       <c r="CS77" s="15">
         <v>7.5559092424884966</v>
@@ -12108,13 +12110,13 @@
         <v>12.143338690828998</v>
       </c>
       <c r="CU77" s="15">
-        <v>10.056550773859982</v>
+        <v>9.8056965461091181</v>
       </c>
       <c r="CV77" s="15">
-        <v>10.219360985153799</v>
+        <v>10.464636659069441</v>
       </c>
       <c r="CW77" s="15">
-        <v>11.305433149113185</v>
+        <v>12.156264138439894</v>
       </c>
       <c r="CX77" s="17"/>
       <c r="CY77" s="17"/>
@@ -12478,10 +12480,10 @@
         <v>12.208299179751123</v>
       </c>
       <c r="CR78" s="15">
-        <v>12.763048877285897</v>
+        <v>13.079489953579483</v>
       </c>
       <c r="CS78" s="15">
-        <v>13.251120832429692</v>
+        <v>15.368336894522884</v>
       </c>
       <c r="CT78" s="15">
         <v>10.979331861107312</v>
@@ -12490,10 +12492,10 @@
         <v>17.699793275597159</v>
       </c>
       <c r="CV78" s="15">
-        <v>14.421952408163307</v>
+        <v>14.440372289855802</v>
       </c>
       <c r="CW78" s="15">
-        <v>13.697033315075061</v>
+        <v>13.984267334446329</v>
       </c>
       <c r="CX78" s="17"/>
       <c r="CY78" s="17"/>
@@ -13033,22 +13035,22 @@
         <v>7.9820565015633349</v>
       </c>
       <c r="CR80" s="15">
-        <v>9.099332452609417</v>
+        <v>9.0524393580900977</v>
       </c>
       <c r="CS80" s="15">
-        <v>8.270384262022759</v>
+        <v>8.3403392801194798</v>
       </c>
       <c r="CT80" s="15">
-        <v>6.8627880815824938</v>
+        <v>6.8659708173381517</v>
       </c>
       <c r="CU80" s="15">
-        <v>5.4002844034027646</v>
+        <v>5.4702591635106046</v>
       </c>
       <c r="CV80" s="15">
-        <v>5.4380924360677199</v>
+        <v>5.5039143382809641</v>
       </c>
       <c r="CW80" s="15">
-        <v>5.5686422571983485</v>
+        <v>5.5997727947111144</v>
       </c>
       <c r="CX80" s="17"/>
       <c r="CY80" s="17"/>
@@ -13604,7 +13606,7 @@
     </row>
     <row r="86" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CX86" s="6"/>
       <c r="CY86" s="6"/>
@@ -13628,7 +13630,7 @@
     </row>
     <row r="89" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="CX89" s="6"/>
       <c r="CY89" s="6"/>
@@ -14425,19 +14427,19 @@
         <v>121.51733250596106</v>
       </c>
       <c r="CW95" s="15">
-        <v>123.50943267996169</v>
+        <v>123.50943267996171</v>
       </c>
       <c r="CX95" s="15">
-        <v>126.025370664165</v>
+        <v>126.0160276011447</v>
       </c>
       <c r="CY95" s="15">
-        <v>126.56740028069215</v>
+        <v>126.55598198964026</v>
       </c>
       <c r="CZ95" s="15">
-        <v>123.15288071253863</v>
+        <v>123.13339008290932</v>
       </c>
       <c r="DA95" s="15">
-        <v>125.54629736377085</v>
+        <v>125.52673725267867</v>
       </c>
       <c r="DB95" s="10"/>
       <c r="DC95" s="10"/>
@@ -14813,22 +14815,22 @@
         <v>123.28877026391771</v>
       </c>
       <c r="CV96" s="15">
-        <v>119.81642239483375</v>
+        <v>119.81642239483376</v>
       </c>
       <c r="CW96" s="15">
-        <v>122.49976029296357</v>
+        <v>122.49976029296359</v>
       </c>
       <c r="CX96" s="15">
-        <v>124.45230476834479</v>
+        <v>124.44128368214609</v>
       </c>
       <c r="CY96" s="15">
-        <v>124.85755499499747</v>
+        <v>124.84141753052849</v>
       </c>
       <c r="CZ96" s="15">
-        <v>121.3990949383206</v>
+        <v>121.37635174077413</v>
       </c>
       <c r="DA96" s="15">
-        <v>124.50421964494632</v>
+        <v>124.48218268872679</v>
       </c>
       <c r="DB96" s="10"/>
       <c r="DC96" s="10"/>
@@ -15210,16 +15212,16 @@
         <v>121.04070789540809</v>
       </c>
       <c r="CX97" s="15">
-        <v>127.87403119918706</v>
+        <v>127.85816015171541</v>
       </c>
       <c r="CY97" s="15">
-        <v>121.86589265206993</v>
+        <v>121.84589948550368</v>
       </c>
       <c r="CZ97" s="15">
-        <v>120.07930329006879</v>
+        <v>120.0470254630014</v>
       </c>
       <c r="DA97" s="15">
-        <v>123.02130615970796</v>
+        <v>122.98982876821665</v>
       </c>
       <c r="DB97" s="10"/>
       <c r="DC97" s="10"/>
@@ -15595,22 +15597,22 @@
         <v>127.42752248454975</v>
       </c>
       <c r="CV98" s="15">
-        <v>121.93860795473164</v>
+        <v>121.93860795473171</v>
       </c>
       <c r="CW98" s="15">
-        <v>124.27638425798749</v>
+        <v>124.27638425798746</v>
       </c>
       <c r="CX98" s="15">
-        <v>126.31227072060234</v>
+        <v>126.27338072675096</v>
       </c>
       <c r="CY98" s="15">
-        <v>128.76445354432835</v>
+        <v>128.72225039938365</v>
       </c>
       <c r="CZ98" s="15">
-        <v>123.32498818686193</v>
+        <v>123.24431875163174</v>
       </c>
       <c r="DA98" s="15">
-        <v>126.26314702842927</v>
+        <v>126.18899456662027</v>
       </c>
       <c r="DB98" s="10"/>
       <c r="DC98" s="10"/>
@@ -16166,22 +16168,22 @@
         <v>123.99314041686364</v>
       </c>
       <c r="CV100" s="15">
-        <v>120.71928245890875</v>
+        <v>120.71950096627016</v>
       </c>
       <c r="CW100" s="15">
-        <v>122.89534996660178</v>
+        <v>122.89506669903689</v>
       </c>
       <c r="CX100" s="15">
-        <v>125.87823128493612</v>
+        <v>125.86616519586404</v>
       </c>
       <c r="CY100" s="15">
-        <v>125.56588825333917</v>
+        <v>125.55216568599792</v>
       </c>
       <c r="CZ100" s="15">
-        <v>122.30685871113445</v>
+        <v>122.28094351306748</v>
       </c>
       <c r="DA100" s="15">
-        <v>124.90321375771252</v>
+        <v>124.87885012824573</v>
       </c>
       <c r="DB100" s="10"/>
       <c r="DC100" s="10"/>
@@ -16382,7 +16384,7 @@
     </row>
     <row r="107" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="109" spans="1:179" x14ac:dyDescent="0.2">
@@ -16392,7 +16394,7 @@
     </row>
     <row r="110" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="111" spans="1:179" x14ac:dyDescent="0.2">
@@ -17178,22 +17180,22 @@
         <v>49.396272026727566</v>
       </c>
       <c r="CV116" s="15">
-        <v>56.416694230029371</v>
+        <v>56.440851530309999</v>
       </c>
       <c r="CW116" s="15">
-        <v>48.659862026449801</v>
+        <v>48.441552181304658</v>
       </c>
       <c r="CX116" s="15">
-        <v>60.086337777171842</v>
+        <v>60.079654013220932</v>
       </c>
       <c r="CY116" s="15">
-        <v>48.243474278867076</v>
+        <v>48.322997338702635</v>
       </c>
       <c r="CZ116" s="15">
-        <v>55.830776355475464</v>
+        <v>55.823691794672506</v>
       </c>
       <c r="DA116" s="15">
-        <v>48.177019372964338</v>
+        <v>48.201573748024742</v>
       </c>
       <c r="DB116" s="10"/>
       <c r="DC116" s="10"/>
@@ -17569,22 +17571,22 @@
         <v>34.063375809105246</v>
       </c>
       <c r="CV117" s="15">
-        <v>26.917437276300898</v>
+        <v>26.837186904821447</v>
       </c>
       <c r="CW117" s="15">
-        <v>32.717542987526713</v>
+        <v>32.842483729749489</v>
       </c>
       <c r="CX117" s="15">
-        <v>23.410583326291775</v>
+        <v>23.419123377041089</v>
       </c>
       <c r="CY117" s="15">
-        <v>34.089879346351104</v>
+        <v>34.049954732605812</v>
       </c>
       <c r="CZ117" s="15">
-        <v>26.564721644270723</v>
+        <v>26.498270782456608</v>
       </c>
       <c r="DA117" s="15">
-        <v>32.062415583710028</v>
+        <v>31.826165375360866</v>
       </c>
       <c r="DB117" s="10"/>
       <c r="DC117" s="10"/>
@@ -17960,22 +17962,22 @@
         <v>10.882193762622057</v>
       </c>
       <c r="CV118" s="15">
-        <v>11.787163071170797</v>
+        <v>11.827470389585434</v>
       </c>
       <c r="CW118" s="15">
-        <v>12.983693537437514</v>
+        <v>12.975339914646048</v>
       </c>
       <c r="CX118" s="15">
-        <v>11.614843439996767</v>
+        <v>11.61416927008292</v>
       </c>
       <c r="CY118" s="15">
-        <v>11.361898049378077</v>
+        <v>11.327859147065835</v>
       </c>
       <c r="CZ118" s="15">
-        <v>12.319415582725794</v>
+        <v>12.380639888670423</v>
       </c>
       <c r="DA118" s="15">
-        <v>13.689588716275795</v>
+        <v>13.780424475138805</v>
       </c>
       <c r="DB118" s="10"/>
       <c r="DC118" s="10"/>
@@ -18351,22 +18353,22 @@
         <v>5.6581584015451343</v>
       </c>
       <c r="CV119" s="15">
-        <v>4.8787054224989221</v>
+        <v>4.8944911752831235</v>
       </c>
       <c r="CW119" s="15">
-        <v>5.6389014485859725</v>
+        <v>5.7406241742997954</v>
       </c>
       <c r="CX119" s="15">
-        <v>4.8882354565396238</v>
+        <v>4.8870533396550604</v>
       </c>
       <c r="CY119" s="15">
-        <v>6.3047483254037529</v>
+        <v>6.2991887816257144</v>
       </c>
       <c r="CZ119" s="15">
-        <v>5.2850864175280217</v>
+        <v>5.2973975342004556</v>
       </c>
       <c r="DA119" s="15">
-        <v>6.0709763270498298</v>
+        <v>6.1918364014755758</v>
       </c>
       <c r="DB119" s="10"/>
       <c r="DC119" s="10"/>
@@ -19498,7 +19500,7 @@
     </row>
     <row r="128" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="130" spans="1:179" x14ac:dyDescent="0.2">
@@ -19508,7 +19510,7 @@
     </row>
     <row r="131" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="132" spans="1:179" x14ac:dyDescent="0.2">
@@ -20294,22 +20296,22 @@
         <v>49.024786660944748</v>
       </c>
       <c r="CV137" s="15">
-        <v>56.046184570573168</v>
+        <v>56.070284710340637</v>
       </c>
       <c r="CW137" s="15">
-        <v>48.417927629565725</v>
+        <v>48.200592109854043</v>
       </c>
       <c r="CX137" s="15">
-        <v>60.016184708832689</v>
+        <v>60.008205312367181</v>
       </c>
       <c r="CY137" s="15">
-        <v>47.861729693575548</v>
+        <v>47.939709154241896</v>
       </c>
       <c r="CZ137" s="15">
-        <v>55.447236280091751</v>
+        <v>55.437227046530403</v>
       </c>
       <c r="DA137" s="15">
-        <v>47.930243068142389</v>
+        <v>47.952788670899018</v>
       </c>
       <c r="DB137" s="10"/>
       <c r="DC137" s="10"/>
@@ -20685,22 +20687,22 @@
         <v>34.257985790023646</v>
       </c>
       <c r="CV138" s="15">
-        <v>27.120269898559734</v>
+        <v>27.039463754079325</v>
       </c>
       <c r="CW138" s="15">
-        <v>32.823198068987502</v>
+        <v>32.948466338847489</v>
       </c>
       <c r="CX138" s="15">
-        <v>23.678812762427707</v>
+        <v>23.687277762627946</v>
       </c>
       <c r="CY138" s="15">
-        <v>34.283275695613625</v>
+        <v>34.243808206867257</v>
       </c>
       <c r="CZ138" s="15">
-        <v>26.76335979685172</v>
+        <v>26.695756679717757</v>
       </c>
       <c r="DA138" s="15">
-        <v>32.165164832654717</v>
+        <v>31.927580720565075</v>
       </c>
       <c r="DB138" s="10"/>
       <c r="DC138" s="10"/>
@@ -21076,22 +21078,22 @@
         <v>11.211565855980107</v>
       </c>
       <c r="CV139" s="15">
-        <v>12.003624738667332</v>
+        <v>12.044694069618645</v>
       </c>
       <c r="CW139" s="15">
-        <v>13.18263573376724</v>
+        <v>13.174123747119923</v>
       </c>
       <c r="CX139" s="15">
-        <v>11.433564228540023</v>
+        <v>11.433223708415548</v>
       </c>
       <c r="CY139" s="15">
-        <v>11.70685898873451</v>
+        <v>11.67242602751079</v>
       </c>
       <c r="CZ139" s="15">
-        <v>12.547949395079543</v>
+        <v>12.611027395666113</v>
       </c>
       <c r="DA139" s="15">
-        <v>13.899003994189293</v>
+        <v>13.992080320540975</v>
       </c>
       <c r="DB139" s="10"/>
       <c r="DC139" s="10"/>
@@ -21467,22 +21469,22 @@
         <v>5.5056616930514872</v>
       </c>
       <c r="CV140" s="15">
-        <v>4.8299207921997906</v>
+        <v>4.8455574659614129</v>
       </c>
       <c r="CW140" s="15">
-        <v>5.5762385676795283</v>
+        <v>5.6768178041785395</v>
       </c>
       <c r="CX140" s="15">
-        <v>4.8714383001995785</v>
+        <v>4.871293216589323</v>
       </c>
       <c r="CY140" s="15">
-        <v>6.1481356220763059</v>
+        <v>6.1440566113800461</v>
       </c>
       <c r="CZ140" s="15">
-        <v>5.2414545279769831</v>
+        <v>5.2559888780857298</v>
       </c>
       <c r="DA140" s="15">
-        <v>6.0055881050135937</v>
+        <v>6.1275502879949313</v>
       </c>
       <c r="DB140" s="10"/>
       <c r="DC140" s="10"/>

--- a/Data/National Accounts/PSA-17FIA_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-17FIA_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E883F87-82CF-4DDD-94D9-298E0C981317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B389C2-3CA7-447F-A6E1-E1C51868C6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="FIA" sheetId="17" r:id="rId1"/>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">FIA!$A$1:$DA$145</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">FIA!$A$1:$DB$145</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="56">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -692,10 +692,13 @@
     <t>Table 18.7 Gross Value Added in Financial and Insurance Activities, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of May 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>Q1 2000 to Q1 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1194,8 +1197,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="49.28515625" style="5" customWidth="1"/>
-    <col min="2" max="105" width="13" style="5" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="5"/>
+    <col min="2" max="106" width="13" style="5" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1210,7 +1213,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1220,7 +1223,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -1386,6 +1389,9 @@
       <c r="CY9" s="18"/>
       <c r="CZ9" s="18"/>
       <c r="DA9" s="18"/>
+      <c r="DB9" s="18">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
@@ -1702,6 +1708,9 @@
       </c>
       <c r="DA10" s="14" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="14" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2023,7 +2032,9 @@
       <c r="DA12" s="19">
         <v>385303.36760576011</v>
       </c>
-      <c r="DB12" s="10"/>
+      <c r="DB12" s="19">
+        <v>513546.90011504956</v>
+      </c>
       <c r="DC12" s="10"/>
       <c r="DD12" s="10"/>
       <c r="DE12" s="10"/>
@@ -2414,7 +2425,9 @@
       <c r="DA13" s="19">
         <v>254405.15202279875</v>
       </c>
-      <c r="DB13" s="10"/>
+      <c r="DB13" s="19">
+        <v>198410.27581079563</v>
+      </c>
       <c r="DC13" s="10"/>
       <c r="DD13" s="10"/>
       <c r="DE13" s="10"/>
@@ -2805,7 +2818,9 @@
       <c r="DA14" s="19">
         <v>110154.99172421533</v>
       </c>
-      <c r="DB14" s="10"/>
+      <c r="DB14" s="19">
+        <v>102858.20726948502</v>
+      </c>
       <c r="DC14" s="10"/>
       <c r="DD14" s="10"/>
       <c r="DE14" s="10"/>
@@ -3196,7 +3211,9 @@
       <c r="DA15" s="19">
         <v>49494.969388841491</v>
       </c>
-      <c r="DB15" s="10"/>
+      <c r="DB15" s="19">
+        <v>42482.855050571401</v>
+      </c>
       <c r="DC15" s="10"/>
       <c r="DD15" s="10"/>
       <c r="DE15" s="10"/>
@@ -3767,7 +3784,9 @@
       <c r="DA17" s="20">
         <v>799358.48074161576</v>
       </c>
-      <c r="DB17" s="10"/>
+      <c r="DB17" s="20">
+        <v>857298.23824590154</v>
+      </c>
       <c r="DC17" s="10"/>
       <c r="DD17" s="10"/>
       <c r="DE17" s="10"/>
@@ -3948,6 +3967,7 @@
       <c r="CY18" s="12"/>
       <c r="CZ18" s="12"/>
       <c r="DA18" s="12"/>
+      <c r="DB18" s="12"/>
     </row>
     <row r="19" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
@@ -4326,7 +4346,7 @@
     </row>
     <row r="24" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:179" x14ac:dyDescent="0.2">
@@ -4336,7 +4356,7 @@
     </row>
     <row r="27" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
@@ -4502,6 +4522,9 @@
       <c r="CY30" s="18"/>
       <c r="CZ30" s="18"/>
       <c r="DA30" s="18"/>
+      <c r="DB30" s="18">
+        <v>2026</v>
+      </c>
     </row>
     <row r="31" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
@@ -4818,6 +4841,9 @@
       </c>
       <c r="DA31" s="14" t="s">
         <v>5</v>
+      </c>
+      <c r="DB31" s="14" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -5139,7 +5165,9 @@
       <c r="DA33" s="19">
         <v>306949.24128408189</v>
       </c>
-      <c r="DB33" s="10"/>
+      <c r="DB33" s="19">
+        <v>395854.86515310162</v>
+      </c>
       <c r="DC33" s="10"/>
       <c r="DD33" s="10"/>
       <c r="DE33" s="10"/>
@@ -5530,7 +5558,9 @@
       <c r="DA34" s="19">
         <v>204370.73525530164</v>
       </c>
-      <c r="DB34" s="10"/>
+      <c r="DB34" s="19">
+        <v>154859.02254951381</v>
+      </c>
       <c r="DC34" s="10"/>
       <c r="DD34" s="10"/>
       <c r="DE34" s="10"/>
@@ -5921,7 +5951,9 @@
       <c r="DA35" s="19">
         <v>89564.310177072039</v>
       </c>
-      <c r="DB35" s="10"/>
+      <c r="DB35" s="19">
+        <v>78103.90700618345</v>
+      </c>
       <c r="DC35" s="10"/>
       <c r="DD35" s="10"/>
       <c r="DE35" s="10"/>
@@ -6312,7 +6344,9 @@
       <c r="DA36" s="19">
         <v>39222.889094905258</v>
       </c>
-      <c r="DB36" s="10"/>
+      <c r="DB36" s="19">
+        <v>32586.122914684165</v>
+      </c>
       <c r="DC36" s="10"/>
       <c r="DD36" s="10"/>
       <c r="DE36" s="10"/>
@@ -6883,7 +6917,9 @@
       <c r="DA38" s="20">
         <v>640107.17581136082</v>
       </c>
-      <c r="DB38" s="10"/>
+      <c r="DB38" s="20">
+        <v>661403.91762348299</v>
+      </c>
       <c r="DC38" s="10"/>
       <c r="DD38" s="10"/>
       <c r="DE38" s="10"/>
@@ -7064,6 +7100,7 @@
       <c r="CY39" s="12"/>
       <c r="CZ39" s="12"/>
       <c r="DA39" s="12"/>
+      <c r="DB39" s="12"/>
     </row>
     <row r="40" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A40" s="13" t="s">
@@ -7175,7 +7212,7 @@
       <c r="CY41" s="9"/>
       <c r="CZ41" s="9"/>
       <c r="DA41" s="9"/>
-      <c r="DB41" s="10"/>
+      <c r="DB41" s="9"/>
       <c r="DC41" s="10"/>
       <c r="DD41" s="10"/>
       <c r="DE41" s="10"/>
@@ -7355,7 +7392,7 @@
       <c r="CY42" s="9"/>
       <c r="CZ42" s="9"/>
       <c r="DA42" s="9"/>
-      <c r="DB42" s="10"/>
+      <c r="DB42" s="9"/>
       <c r="DC42" s="10"/>
       <c r="DD42" s="10"/>
       <c r="DE42" s="10"/>
@@ -7438,6 +7475,7 @@
       <c r="CY43" s="6"/>
       <c r="CZ43" s="6"/>
       <c r="DA43" s="6"/>
+      <c r="DB43" s="6"/>
     </row>
     <row r="44" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
@@ -7447,15 +7485,17 @@
       <c r="CY44" s="6"/>
       <c r="CZ44" s="6"/>
       <c r="DA44" s="6"/>
+      <c r="DB44" s="6"/>
     </row>
     <row r="45" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="CX45" s="6"/>
       <c r="CY45" s="6"/>
       <c r="CZ45" s="6"/>
       <c r="DA45" s="6"/>
+      <c r="DB45" s="6"/>
     </row>
     <row r="46" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT46" s="8"/>
@@ -7465,6 +7505,7 @@
       <c r="CY46" s="6"/>
       <c r="CZ46" s="6"/>
       <c r="DA46" s="6"/>
+      <c r="DB46" s="6"/>
     </row>
     <row r="47" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
@@ -7477,10 +7518,11 @@
       <c r="CY47" s="6"/>
       <c r="CZ47" s="6"/>
       <c r="DA47" s="6"/>
+      <c r="DB47" s="6"/>
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CT48" s="8"/>
       <c r="CU48" s="8"/>
@@ -7489,6 +7531,7 @@
       <c r="CY48" s="6"/>
       <c r="CZ48" s="6"/>
       <c r="DA48" s="6"/>
+      <c r="DB48" s="6"/>
     </row>
     <row r="49" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
@@ -7498,12 +7541,14 @@
       <c r="CY49" s="6"/>
       <c r="CZ49" s="6"/>
       <c r="DA49" s="6"/>
+      <c r="DB49" s="6"/>
     </row>
     <row r="50" spans="1:175" x14ac:dyDescent="0.2">
       <c r="CX50" s="6"/>
       <c r="CY50" s="6"/>
       <c r="CZ50" s="6"/>
       <c r="DA50" s="6"/>
+      <c r="DB50" s="6"/>
     </row>
     <row r="51" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="16"/>
@@ -7657,10 +7702,13 @@
       <c r="CU51" s="18"/>
       <c r="CV51" s="18"/>
       <c r="CW51" s="18"/>
-      <c r="CX51" s="21"/>
+      <c r="CX51" s="18" t="s">
+        <v>55</v>
+      </c>
       <c r="CY51" s="21"/>
       <c r="CZ51" s="21"/>
       <c r="DA51" s="21"/>
+      <c r="DB51" s="21"/>
     </row>
     <row r="52" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
@@ -7966,17 +8014,20 @@
       <c r="CW52" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="CX52" s="22"/>
+      <c r="CX52" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="CY52" s="22"/>
       <c r="CZ52" s="22"/>
       <c r="DA52" s="22"/>
+      <c r="DB52" s="22"/>
     </row>
     <row r="53" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8"/>
-      <c r="CX53" s="6"/>
       <c r="CY53" s="6"/>
       <c r="CZ53" s="6"/>
       <c r="DA53" s="6"/>
+      <c r="DB53" s="6"/>
     </row>
     <row r="54" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
@@ -8282,11 +8333,13 @@
       <c r="CW54" s="15">
         <v>6.7727903869671593</v>
       </c>
-      <c r="CX54" s="17"/>
+      <c r="CX54" s="15">
+        <v>6.203607417561031</v>
+      </c>
       <c r="CY54" s="17"/>
       <c r="CZ54" s="17"/>
       <c r="DA54" s="17"/>
-      <c r="DB54" s="10"/>
+      <c r="DB54" s="17"/>
       <c r="DC54" s="10"/>
       <c r="DD54" s="10"/>
       <c r="DE54" s="10"/>
@@ -8661,11 +8714,13 @@
       <c r="CW55" s="15">
         <v>3.983815008488051</v>
       </c>
-      <c r="CX55" s="17"/>
+      <c r="CX55" s="15">
+        <v>5.2640573977278393</v>
+      </c>
       <c r="CY55" s="17"/>
       <c r="CZ55" s="17"/>
       <c r="DA55" s="17"/>
-      <c r="DB55" s="10"/>
+      <c r="DB55" s="17"/>
       <c r="DC55" s="10"/>
       <c r="DD55" s="10"/>
       <c r="DE55" s="10"/>
@@ -9040,11 +9095,13 @@
       <c r="CW56" s="15">
         <v>13.962318640676969</v>
       </c>
-      <c r="CX56" s="17"/>
+      <c r="CX56" s="15">
+        <v>10.036654773695645</v>
+      </c>
       <c r="CY56" s="17"/>
       <c r="CZ56" s="17"/>
       <c r="DA56" s="17"/>
-      <c r="DB56" s="10"/>
+      <c r="DB56" s="17"/>
       <c r="DC56" s="10"/>
       <c r="DD56" s="10"/>
       <c r="DE56" s="10"/>
@@ -9419,11 +9476,13 @@
       <c r="CW57" s="15">
         <v>15.738482232373002</v>
       </c>
-      <c r="CX57" s="17"/>
+      <c r="CX57" s="15">
+        <v>8.0073215312359736</v>
+      </c>
       <c r="CY57" s="17"/>
       <c r="CZ57" s="17"/>
       <c r="DA57" s="17"/>
-      <c r="DB57" s="10"/>
+      <c r="DB57" s="17"/>
       <c r="DC57" s="10"/>
       <c r="DD57" s="10"/>
       <c r="DE57" s="10"/>
@@ -9595,11 +9654,11 @@
       <c r="CU58" s="10"/>
       <c r="CV58" s="10"/>
       <c r="CW58" s="10"/>
-      <c r="CX58" s="9"/>
+      <c r="CX58" s="10"/>
       <c r="CY58" s="9"/>
       <c r="CZ58" s="9"/>
       <c r="DA58" s="9"/>
-      <c r="DB58" s="10"/>
+      <c r="DB58" s="9"/>
       <c r="DC58" s="10"/>
       <c r="DD58" s="10"/>
       <c r="DE58" s="10"/>
@@ -9974,11 +10033,13 @@
       <c r="CW59" s="15">
         <v>7.3043740047124004</v>
       </c>
-      <c r="CX59" s="17"/>
+      <c r="CX59" s="15">
+        <v>6.5168981182013539</v>
+      </c>
       <c r="CY59" s="17"/>
       <c r="CZ59" s="17"/>
       <c r="DA59" s="17"/>
-      <c r="DB59" s="10"/>
+      <c r="DB59" s="17"/>
       <c r="DC59" s="10"/>
       <c r="DD59" s="10"/>
       <c r="DE59" s="10"/>
@@ -10151,19 +10212,20 @@
       <c r="CU60" s="12"/>
       <c r="CV60" s="12"/>
       <c r="CW60" s="12"/>
-      <c r="CX60" s="23"/>
+      <c r="CX60" s="12"/>
       <c r="CY60" s="23"/>
       <c r="CZ60" s="23"/>
       <c r="DA60" s="23"/>
+      <c r="DB60" s="23"/>
     </row>
     <row r="61" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A61" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CX61" s="6"/>
       <c r="CY61" s="6"/>
       <c r="CZ61" s="6"/>
       <c r="DA61" s="6"/>
+      <c r="DB61" s="6"/>
     </row>
     <row r="62" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="10"/>
@@ -10266,11 +10328,11 @@
       <c r="CU62" s="10"/>
       <c r="CV62" s="10"/>
       <c r="CW62" s="10"/>
-      <c r="CX62" s="9"/>
+      <c r="CX62" s="10"/>
       <c r="CY62" s="9"/>
       <c r="CZ62" s="9"/>
       <c r="DA62" s="9"/>
-      <c r="DB62" s="10"/>
+      <c r="DB62" s="9"/>
       <c r="DC62" s="10"/>
       <c r="DD62" s="10"/>
       <c r="DE62" s="10"/>
@@ -10442,11 +10504,11 @@
       <c r="CU63" s="10"/>
       <c r="CV63" s="10"/>
       <c r="CW63" s="10"/>
-      <c r="CX63" s="9"/>
+      <c r="CX63" s="10"/>
       <c r="CY63" s="9"/>
       <c r="CZ63" s="9"/>
       <c r="DA63" s="9"/>
-      <c r="DB63" s="10"/>
+      <c r="DB63" s="9"/>
       <c r="DC63" s="10"/>
       <c r="DD63" s="10"/>
       <c r="DE63" s="10"/>
@@ -10521,67 +10583,67 @@
       <c r="A64" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="CX64" s="6"/>
       <c r="CY64" s="6"/>
       <c r="CZ64" s="6"/>
       <c r="DA64" s="6"/>
+      <c r="DB64" s="6"/>
     </row>
     <row r="65" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="CX65" s="6"/>
       <c r="CY65" s="6"/>
       <c r="CZ65" s="6"/>
       <c r="DA65" s="6"/>
+      <c r="DB65" s="6"/>
     </row>
     <row r="66" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="CX66" s="6"/>
+        <v>53</v>
+      </c>
       <c r="CY66" s="6"/>
       <c r="CZ66" s="6"/>
       <c r="DA66" s="6"/>
+      <c r="DB66" s="6"/>
     </row>
     <row r="67" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX67" s="6"/>
       <c r="CY67" s="6"/>
       <c r="CZ67" s="6"/>
       <c r="DA67" s="6"/>
+      <c r="DB67" s="6"/>
     </row>
     <row r="68" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="CX68" s="6"/>
       <c r="CY68" s="6"/>
       <c r="CZ68" s="6"/>
       <c r="DA68" s="6"/>
+      <c r="DB68" s="6"/>
     </row>
     <row r="69" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="CX69" s="6"/>
+        <v>54</v>
+      </c>
       <c r="CY69" s="6"/>
       <c r="CZ69" s="6"/>
       <c r="DA69" s="6"/>
+      <c r="DB69" s="6"/>
     </row>
     <row r="70" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="CX70" s="6"/>
       <c r="CY70" s="6"/>
       <c r="CZ70" s="6"/>
       <c r="DA70" s="6"/>
+      <c r="DB70" s="6"/>
     </row>
     <row r="71" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX71" s="6"/>
       <c r="CY71" s="6"/>
       <c r="CZ71" s="6"/>
       <c r="DA71" s="6"/>
+      <c r="DB71" s="6"/>
     </row>
     <row r="72" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="16"/>
@@ -10735,10 +10797,13 @@
       <c r="CU72" s="18"/>
       <c r="CV72" s="18"/>
       <c r="CW72" s="18"/>
-      <c r="CX72" s="21"/>
+      <c r="CX72" s="18" t="s">
+        <v>55</v>
+      </c>
       <c r="CY72" s="21"/>
       <c r="CZ72" s="21"/>
       <c r="DA72" s="21"/>
+      <c r="DB72" s="21"/>
     </row>
     <row r="73" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -11044,17 +11109,20 @@
       <c r="CW73" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="CX73" s="22"/>
+      <c r="CX73" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="CY73" s="22"/>
       <c r="CZ73" s="22"/>
       <c r="DA73" s="22"/>
+      <c r="DB73" s="22"/>
     </row>
     <row r="74" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="8"/>
-      <c r="CX74" s="6"/>
       <c r="CY74" s="6"/>
       <c r="CZ74" s="6"/>
       <c r="DA74" s="6"/>
+      <c r="DB74" s="6"/>
     </row>
     <row r="75" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
@@ -11360,11 +11428,13 @@
       <c r="CW75" s="15">
         <v>5.0568751723798471</v>
       </c>
-      <c r="CX75" s="17"/>
+      <c r="CX75" s="15">
+        <v>3.1622792379500027</v>
+      </c>
       <c r="CY75" s="17"/>
       <c r="CZ75" s="17"/>
       <c r="DA75" s="17"/>
-      <c r="DB75" s="10"/>
+      <c r="DB75" s="17"/>
       <c r="DC75" s="10"/>
       <c r="DD75" s="10"/>
       <c r="DE75" s="10"/>
@@ -11739,11 +11809,13 @@
       <c r="CW76" s="15">
         <v>2.3278363036063752</v>
       </c>
-      <c r="CX76" s="17"/>
+      <c r="CX76" s="15">
+        <v>2.2390819750675632</v>
+      </c>
       <c r="CY76" s="17"/>
       <c r="CZ76" s="17"/>
       <c r="DA76" s="17"/>
-      <c r="DB76" s="10"/>
+      <c r="DB76" s="17"/>
       <c r="DC76" s="10"/>
       <c r="DD76" s="10"/>
       <c r="DE76" s="10"/>
@@ -12118,11 +12190,13 @@
       <c r="CW77" s="15">
         <v>12.156264138439894</v>
       </c>
-      <c r="CX77" s="17"/>
+      <c r="CX77" s="15">
+        <v>6.8315767330937831</v>
+      </c>
       <c r="CY77" s="17"/>
       <c r="CZ77" s="17"/>
       <c r="DA77" s="17"/>
-      <c r="DB77" s="10"/>
+      <c r="DB77" s="17"/>
       <c r="DC77" s="10"/>
       <c r="DD77" s="10"/>
       <c r="DE77" s="10"/>
@@ -12497,11 +12571,13 @@
       <c r="CW78" s="15">
         <v>13.984267334446329</v>
       </c>
-      <c r="CX78" s="17"/>
+      <c r="CX78" s="15">
+        <v>4.6126009133125763</v>
+      </c>
       <c r="CY78" s="17"/>
       <c r="CZ78" s="17"/>
       <c r="DA78" s="17"/>
-      <c r="DB78" s="10"/>
+      <c r="DB78" s="17"/>
       <c r="DC78" s="10"/>
       <c r="DD78" s="10"/>
       <c r="DE78" s="10"/>
@@ -12673,11 +12749,11 @@
       <c r="CU79" s="10"/>
       <c r="CV79" s="10"/>
       <c r="CW79" s="10"/>
-      <c r="CX79" s="9"/>
+      <c r="CX79" s="10"/>
       <c r="CY79" s="9"/>
       <c r="CZ79" s="9"/>
       <c r="DA79" s="9"/>
-      <c r="DB79" s="10"/>
+      <c r="DB79" s="9"/>
       <c r="DC79" s="10"/>
       <c r="DD79" s="10"/>
       <c r="DE79" s="10"/>
@@ -13052,11 +13128,13 @@
       <c r="CW80" s="15">
         <v>5.5997727947111144</v>
       </c>
-      <c r="CX80" s="17"/>
+      <c r="CX80" s="15">
+        <v>3.4337673505317809</v>
+      </c>
       <c r="CY80" s="17"/>
       <c r="CZ80" s="17"/>
       <c r="DA80" s="17"/>
-      <c r="DB80" s="10"/>
+      <c r="DB80" s="17"/>
       <c r="DC80" s="10"/>
       <c r="DD80" s="10"/>
       <c r="DE80" s="10"/>
@@ -13229,19 +13307,20 @@
       <c r="CU81" s="12"/>
       <c r="CV81" s="12"/>
       <c r="CW81" s="12"/>
-      <c r="CX81" s="23"/>
+      <c r="CX81" s="12"/>
       <c r="CY81" s="23"/>
       <c r="CZ81" s="23"/>
       <c r="DA81" s="23"/>
+      <c r="DB81" s="23"/>
     </row>
     <row r="82" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A82" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CX82" s="6"/>
       <c r="CY82" s="6"/>
       <c r="CZ82" s="6"/>
       <c r="DA82" s="6"/>
+      <c r="DB82" s="6"/>
     </row>
     <row r="83" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" s="10"/>
@@ -13348,7 +13427,7 @@
       <c r="CY83" s="9"/>
       <c r="CZ83" s="9"/>
       <c r="DA83" s="9"/>
-      <c r="DB83" s="10"/>
+      <c r="DB83" s="9"/>
       <c r="DC83" s="10"/>
       <c r="DD83" s="10"/>
       <c r="DE83" s="10"/>
@@ -13524,7 +13603,7 @@
       <c r="CY84" s="9"/>
       <c r="CZ84" s="9"/>
       <c r="DA84" s="9"/>
-      <c r="DB84" s="10"/>
+      <c r="DB84" s="9"/>
       <c r="DC84" s="10"/>
       <c r="DD84" s="10"/>
       <c r="DE84" s="10"/>
@@ -13603,21 +13682,24 @@
       <c r="CY85" s="6"/>
       <c r="CZ85" s="6"/>
       <c r="DA85" s="6"/>
+      <c r="DB85" s="6"/>
     </row>
     <row r="86" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="CX86" s="6"/>
       <c r="CY86" s="6"/>
       <c r="CZ86" s="6"/>
       <c r="DA86" s="6"/>
+      <c r="DB86" s="6"/>
     </row>
     <row r="87" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CX87" s="6"/>
       <c r="CY87" s="6"/>
       <c r="CZ87" s="6"/>
       <c r="DA87" s="6"/>
+      <c r="DB87" s="6"/>
     </row>
     <row r="88" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
@@ -13627,15 +13709,17 @@
       <c r="CY88" s="6"/>
       <c r="CZ88" s="6"/>
       <c r="DA88" s="6"/>
+      <c r="DB88" s="6"/>
     </row>
     <row r="89" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CX89" s="6"/>
       <c r="CY89" s="6"/>
       <c r="CZ89" s="6"/>
       <c r="DA89" s="6"/>
+      <c r="DB89" s="6"/>
     </row>
     <row r="90" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
@@ -13645,6 +13729,7 @@
       <c r="CY90" s="6"/>
       <c r="CZ90" s="6"/>
       <c r="DA90" s="6"/>
+      <c r="DB90" s="6"/>
     </row>
     <row r="92" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="16"/>
@@ -13804,6 +13889,9 @@
       <c r="CY92" s="18"/>
       <c r="CZ92" s="18"/>
       <c r="DA92" s="18"/>
+      <c r="DB92" s="18">
+        <v>2026</v>
+      </c>
     </row>
     <row r="93" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A93" s="7" t="s">
@@ -14120,6 +14208,9 @@
       </c>
       <c r="DA93" s="14" t="s">
         <v>5</v>
+      </c>
+      <c r="DB93" s="14" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -14441,7 +14532,9 @@
       <c r="DA95" s="15">
         <v>125.52673725267867</v>
       </c>
-      <c r="DB95" s="10"/>
+      <c r="DB95" s="15">
+        <v>129.73110736340934</v>
+      </c>
       <c r="DC95" s="10"/>
       <c r="DD95" s="10"/>
       <c r="DE95" s="10"/>
@@ -14832,7 +14925,9 @@
       <c r="DA96" s="15">
         <v>124.48218268872679</v>
       </c>
-      <c r="DB96" s="10"/>
+      <c r="DB96" s="15">
+        <v>128.12316166296154</v>
+      </c>
       <c r="DC96" s="10"/>
       <c r="DD96" s="10"/>
       <c r="DE96" s="10"/>
@@ -15223,7 +15318,9 @@
       <c r="DA97" s="15">
         <v>122.98982876821665</v>
       </c>
-      <c r="DB97" s="10"/>
+      <c r="DB97" s="15">
+        <v>131.69406142683974</v>
+      </c>
       <c r="DC97" s="10"/>
       <c r="DD97" s="10"/>
       <c r="DE97" s="10"/>
@@ -15614,7 +15711,9 @@
       <c r="DA98" s="15">
         <v>126.18899456662027</v>
       </c>
-      <c r="DB98" s="10"/>
+      <c r="DB98" s="15">
+        <v>130.37100228768702</v>
+      </c>
       <c r="DC98" s="10"/>
       <c r="DD98" s="10"/>
       <c r="DE98" s="10"/>
@@ -16185,7 +16284,9 @@
       <c r="DA100" s="15">
         <v>124.87885012824573</v>
       </c>
-      <c r="DB100" s="10"/>
+      <c r="DB100" s="15">
+        <v>129.61795589694938</v>
+      </c>
       <c r="DC100" s="10"/>
       <c r="DD100" s="10"/>
       <c r="DE100" s="10"/>
@@ -16366,6 +16467,7 @@
       <c r="CY101" s="12"/>
       <c r="CZ101" s="12"/>
       <c r="DA101" s="12"/>
+      <c r="DB101" s="12"/>
     </row>
     <row r="102" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A102" s="13" t="s">
@@ -16384,7 +16486,7 @@
     </row>
     <row r="107" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="109" spans="1:179" x14ac:dyDescent="0.2">
@@ -16394,7 +16496,7 @@
     </row>
     <row r="110" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="111" spans="1:179" x14ac:dyDescent="0.2">
@@ -16560,6 +16662,9 @@
       <c r="CY113" s="18"/>
       <c r="CZ113" s="18"/>
       <c r="DA113" s="18"/>
+      <c r="DB113" s="18">
+        <v>2026</v>
+      </c>
     </row>
     <row r="114" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A114" s="7" t="s">
@@ -16876,6 +16981,9 @@
       </c>
       <c r="DA114" s="14" t="s">
         <v>5</v>
+      </c>
+      <c r="DB114" s="14" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -17197,7 +17305,9 @@
       <c r="DA116" s="15">
         <v>48.201573748024742</v>
       </c>
-      <c r="DB116" s="10"/>
+      <c r="DB116" s="15">
+        <v>59.902945929972539</v>
+      </c>
       <c r="DC116" s="10"/>
       <c r="DD116" s="10"/>
       <c r="DE116" s="10"/>
@@ -17588,7 +17698,9 @@
       <c r="DA117" s="15">
         <v>31.826165375360866</v>
       </c>
-      <c r="DB117" s="10"/>
+      <c r="DB117" s="15">
+        <v>23.14367007411078</v>
+      </c>
       <c r="DC117" s="10"/>
       <c r="DD117" s="10"/>
       <c r="DE117" s="10"/>
@@ -17979,7 +18091,9 @@
       <c r="DA118" s="15">
         <v>13.780424475138805</v>
       </c>
-      <c r="DB118" s="10"/>
+      <c r="DB118" s="15">
+        <v>11.997949217758906</v>
+      </c>
       <c r="DC118" s="10"/>
       <c r="DD118" s="10"/>
       <c r="DE118" s="10"/>
@@ -18370,7 +18484,9 @@
       <c r="DA119" s="15">
         <v>6.1918364014755758</v>
       </c>
-      <c r="DB119" s="10"/>
+      <c r="DB119" s="15">
+        <v>4.9554347781577865</v>
+      </c>
       <c r="DC119" s="10"/>
       <c r="DD119" s="10"/>
       <c r="DE119" s="10"/>
@@ -18550,7 +18666,7 @@
       <c r="CY120" s="15"/>
       <c r="CZ120" s="15"/>
       <c r="DA120" s="15"/>
-      <c r="DB120" s="10"/>
+      <c r="DB120" s="15"/>
       <c r="DC120" s="10"/>
       <c r="DD120" s="10"/>
       <c r="DE120" s="10"/>
@@ -18941,7 +19057,9 @@
       <c r="DA121" s="15">
         <v>100</v>
       </c>
-      <c r="DB121" s="10"/>
+      <c r="DB121" s="15">
+        <v>100</v>
+      </c>
       <c r="DC121" s="10"/>
       <c r="DD121" s="10"/>
       <c r="DE121" s="10"/>
@@ -19122,6 +19240,7 @@
       <c r="CY122" s="12"/>
       <c r="CZ122" s="12"/>
       <c r="DA122" s="12"/>
+      <c r="DB122" s="12"/>
     </row>
     <row r="123" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A123" s="13" t="s">
@@ -19500,7 +19619,7 @@
     </row>
     <row r="128" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="130" spans="1:179" x14ac:dyDescent="0.2">
@@ -19510,7 +19629,7 @@
     </row>
     <row r="131" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="132" spans="1:179" x14ac:dyDescent="0.2">
@@ -19676,6 +19795,9 @@
       <c r="CY134" s="18"/>
       <c r="CZ134" s="18"/>
       <c r="DA134" s="18"/>
+      <c r="DB134" s="18">
+        <v>2026</v>
+      </c>
     </row>
     <row r="135" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A135" s="7" t="s">
@@ -19992,6 +20114,9 @@
       </c>
       <c r="DA135" s="14" t="s">
         <v>5</v>
+      </c>
+      <c r="DB135" s="14" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -20313,7 +20438,9 @@
       <c r="DA137" s="15">
         <v>47.952788670899018</v>
       </c>
-      <c r="DB137" s="10"/>
+      <c r="DB137" s="15">
+        <v>59.850698583017724</v>
+      </c>
       <c r="DC137" s="10"/>
       <c r="DD137" s="10"/>
       <c r="DE137" s="10"/>
@@ -20704,7 +20831,9 @@
       <c r="DA138" s="15">
         <v>31.927580720565075</v>
       </c>
-      <c r="DB138" s="10"/>
+      <c r="DB138" s="15">
+        <v>23.413683896210351</v>
+      </c>
       <c r="DC138" s="10"/>
       <c r="DD138" s="10"/>
       <c r="DE138" s="10"/>
@@ -21095,7 +21224,9 @@
       <c r="DA139" s="15">
         <v>13.992080320540975</v>
       </c>
-      <c r="DB139" s="10"/>
+      <c r="DB139" s="15">
+        <v>11.808806226431457</v>
+      </c>
       <c r="DC139" s="10"/>
       <c r="DD139" s="10"/>
       <c r="DE139" s="10"/>
@@ -21486,7 +21617,9 @@
       <c r="DA140" s="15">
         <v>6.1275502879949313</v>
       </c>
-      <c r="DB140" s="10"/>
+      <c r="DB140" s="15">
+        <v>4.9268112943404798</v>
+      </c>
       <c r="DC140" s="10"/>
       <c r="DD140" s="10"/>
       <c r="DE140" s="10"/>
@@ -22057,7 +22190,9 @@
       <c r="DA142" s="15">
         <v>100</v>
       </c>
-      <c r="DB142" s="10"/>
+      <c r="DB142" s="15">
+        <v>100</v>
+      </c>
       <c r="DC142" s="10"/>
       <c r="DD142" s="10"/>
       <c r="DE142" s="10"/>
@@ -22238,22 +22373,25 @@
       <c r="CY143" s="12"/>
       <c r="CZ143" s="12"/>
       <c r="DA143" s="12"/>
+      <c r="DB143" s="12"/>
     </row>
     <row r="144" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A144" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="146" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CZ146" s="8"/>
       <c r="DA146" s="8"/>
+      <c r="DB146" s="8"/>
     </row>
-    <row r="147" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="147" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CV147" s="8"/>
       <c r="CZ147" s="8"/>
       <c r="DA147" s="8"/>
+      <c r="DB147" s="8"/>
     </row>
-    <row r="148" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="148" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CT148" s="8"/>
       <c r="CU148" s="8"/>
       <c r="CV148" s="8"/>
@@ -22261,8 +22399,9 @@
       <c r="CY148" s="8"/>
       <c r="CZ148" s="8"/>
       <c r="DA148" s="8"/>
+      <c r="DB148" s="8"/>
     </row>
-    <row r="149" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="149" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CT149" s="8"/>
       <c r="CU149" s="8"/>
       <c r="CV149" s="8"/>
@@ -22270,8 +22409,9 @@
       <c r="CY149" s="8"/>
       <c r="CZ149" s="8"/>
       <c r="DA149" s="8"/>
+      <c r="DB149" s="8"/>
     </row>
-    <row r="150" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="150" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CT150" s="8"/>
       <c r="CU150" s="8"/>
       <c r="CV150" s="8"/>
@@ -22280,7 +22420,7 @@
       <c r="CZ150" s="8"/>
       <c r="DA150" s="8"/>
     </row>
-    <row r="151" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="151" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CT151" s="8"/>
       <c r="CU151" s="8"/>
       <c r="CV151" s="8"/>
@@ -22295,13 +22435,13 @@
   <pageSetup paperSize="9" scale="31" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="42" max="81" man="1"/>
-    <brk id="84" max="81" man="1"/>
-    <brk id="104" max="81" man="1"/>
+    <brk id="42" max="105" man="1"/>
+    <brk id="84" max="105" man="1"/>
+    <brk id="104" max="105" man="1"/>
   </rowBreaks>
   <colBreaks count="2" manualBreakCount="2">
-    <brk id="29" max="164" man="1"/>
-    <brk id="61" max="164" man="1"/>
+    <brk id="29" max="144" man="1"/>
+    <brk id="61" max="144" man="1"/>
   </colBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-17FIA_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-17FIA_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B389C2-3CA7-447F-A6E1-E1C51868C6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB89869-4A41-4F4C-89CA-919549FBFB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">FIA!$A$1:$DB$145</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">FIA!$A$1:$DC$145</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="56">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -692,13 +692,13 @@
     <t>Table 18.7 Gross Value Added in Financial and Insurance Activities, by Industry</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>As of August 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
 </sst>
 </file>
@@ -1197,8 +1197,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="49.28515625" style="5" customWidth="1"/>
-    <col min="2" max="106" width="13" style="5" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="5"/>
+    <col min="2" max="107" width="13" style="5" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1213,7 +1213,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1223,7 +1223,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -1392,6 +1392,7 @@
       <c r="DB9" s="18">
         <v>2026</v>
       </c>
+      <c r="DC9" s="18"/>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
@@ -1711,6 +1712,9 @@
       </c>
       <c r="DB10" s="14" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2033,9 +2037,11 @@
         <v>385303.36760576011</v>
       </c>
       <c r="DB12" s="19">
-        <v>513546.90011504956</v>
-      </c>
-      <c r="DC12" s="10"/>
+        <v>511750.38922568184</v>
+      </c>
+      <c r="DC12" s="19">
+        <v>404852.04095798271</v>
+      </c>
       <c r="DD12" s="10"/>
       <c r="DE12" s="10"/>
       <c r="DF12" s="10"/>
@@ -2426,9 +2432,11 @@
         <v>254405.15202279875</v>
       </c>
       <c r="DB13" s="19">
-        <v>198410.27581079563</v>
-      </c>
-      <c r="DC13" s="10"/>
+        <v>200791.06916151836</v>
+      </c>
+      <c r="DC13" s="19">
+        <v>285286.21173047845</v>
+      </c>
       <c r="DD13" s="10"/>
       <c r="DE13" s="10"/>
       <c r="DF13" s="10"/>
@@ -2819,9 +2827,11 @@
         <v>110154.99172421533</v>
       </c>
       <c r="DB14" s="19">
-        <v>102858.20726948502</v>
-      </c>
-      <c r="DC14" s="10"/>
+        <v>101536.84993782337</v>
+      </c>
+      <c r="DC14" s="19">
+        <v>98883.625801375834</v>
+      </c>
       <c r="DD14" s="10"/>
       <c r="DE14" s="10"/>
       <c r="DF14" s="10"/>
@@ -3212,9 +3222,11 @@
         <v>49494.969388841491</v>
       </c>
       <c r="DB15" s="19">
-        <v>42482.855050571401</v>
-      </c>
-      <c r="DC15" s="10"/>
+        <v>43832.578741009274</v>
+      </c>
+      <c r="DC15" s="19">
+        <v>51419.329155110114</v>
+      </c>
       <c r="DD15" s="10"/>
       <c r="DE15" s="10"/>
       <c r="DF15" s="10"/>
@@ -3785,9 +3797,11 @@
         <v>799358.48074161576</v>
       </c>
       <c r="DB17" s="20">
-        <v>857298.23824590154</v>
-      </c>
-      <c r="DC17" s="10"/>
+        <v>857910.88706603285</v>
+      </c>
+      <c r="DC17" s="20">
+        <v>840441.20764494711</v>
+      </c>
       <c r="DD17" s="10"/>
       <c r="DE17" s="10"/>
       <c r="DF17" s="10"/>
@@ -3968,6 +3982,7 @@
       <c r="CZ18" s="12"/>
       <c r="DA18" s="12"/>
       <c r="DB18" s="12"/>
+      <c r="DC18" s="12"/>
     </row>
     <row r="19" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
@@ -4346,7 +4361,7 @@
     </row>
     <row r="24" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:179" x14ac:dyDescent="0.2">
@@ -4356,7 +4371,7 @@
     </row>
     <row r="27" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
@@ -4525,6 +4540,7 @@
       <c r="DB30" s="18">
         <v>2026</v>
       </c>
+      <c r="DC30" s="18"/>
     </row>
     <row r="31" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
@@ -4844,6 +4860,9 @@
       </c>
       <c r="DB31" s="14" t="s">
         <v>2</v>
+      </c>
+      <c r="DC31" s="14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -5166,9 +5185,11 @@
         <v>306949.24128408189</v>
       </c>
       <c r="DB33" s="19">
-        <v>395854.86515310162</v>
-      </c>
-      <c r="DC33" s="10"/>
+        <v>394470.06938138651</v>
+      </c>
+      <c r="DC33" s="19">
+        <v>299557.3910569459</v>
+      </c>
       <c r="DD33" s="10"/>
       <c r="DE33" s="10"/>
       <c r="DF33" s="10"/>
@@ -5559,9 +5580,11 @@
         <v>204370.73525530164</v>
       </c>
       <c r="DB34" s="19">
-        <v>154859.02254951381</v>
-      </c>
-      <c r="DC34" s="10"/>
+        <v>156717.29873681057</v>
+      </c>
+      <c r="DC34" s="19">
+        <v>213969.37630853272</v>
+      </c>
       <c r="DD34" s="10"/>
       <c r="DE34" s="10"/>
       <c r="DF34" s="10"/>
@@ -5952,9 +5975,11 @@
         <v>89564.310177072039</v>
       </c>
       <c r="DB35" s="19">
-        <v>78103.90700618345</v>
-      </c>
-      <c r="DC35" s="10"/>
+        <v>77100.553235067739</v>
+      </c>
+      <c r="DC35" s="19">
+        <v>75989.952545359964</v>
+      </c>
       <c r="DD35" s="10"/>
       <c r="DE35" s="10"/>
       <c r="DF35" s="10"/>
@@ -6345,9 +6370,11 @@
         <v>39222.889094905258</v>
       </c>
       <c r="DB36" s="19">
-        <v>32586.122914684165</v>
-      </c>
-      <c r="DC36" s="10"/>
+        <v>33620.821455681027</v>
+      </c>
+      <c r="DC36" s="19">
+        <v>37410.94609309837</v>
+      </c>
       <c r="DD36" s="10"/>
       <c r="DE36" s="10"/>
       <c r="DF36" s="10"/>
@@ -6918,9 +6945,11 @@
         <v>640107.17581136082</v>
       </c>
       <c r="DB38" s="20">
-        <v>661403.91762348299</v>
-      </c>
-      <c r="DC38" s="10"/>
+        <v>661908.74280894583</v>
+      </c>
+      <c r="DC38" s="20">
+        <v>626927.66600393702</v>
+      </c>
       <c r="DD38" s="10"/>
       <c r="DE38" s="10"/>
       <c r="DF38" s="10"/>
@@ -7101,6 +7130,7 @@
       <c r="CZ39" s="12"/>
       <c r="DA39" s="12"/>
       <c r="DB39" s="12"/>
+      <c r="DC39" s="12"/>
     </row>
     <row r="40" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A40" s="13" t="s">
@@ -7213,7 +7243,7 @@
       <c r="CZ41" s="9"/>
       <c r="DA41" s="9"/>
       <c r="DB41" s="9"/>
-      <c r="DC41" s="10"/>
+      <c r="DC41" s="9"/>
       <c r="DD41" s="10"/>
       <c r="DE41" s="10"/>
       <c r="DF41" s="10"/>
@@ -7393,7 +7423,7 @@
       <c r="CZ42" s="9"/>
       <c r="DA42" s="9"/>
       <c r="DB42" s="9"/>
-      <c r="DC42" s="10"/>
+      <c r="DC42" s="9"/>
       <c r="DD42" s="10"/>
       <c r="DE42" s="10"/>
       <c r="DF42" s="10"/>
@@ -7476,6 +7506,7 @@
       <c r="CZ43" s="6"/>
       <c r="DA43" s="6"/>
       <c r="DB43" s="6"/>
+      <c r="DC43" s="6"/>
     </row>
     <row r="44" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
@@ -7486,16 +7517,18 @@
       <c r="CZ44" s="6"/>
       <c r="DA44" s="6"/>
       <c r="DB44" s="6"/>
+      <c r="DC44" s="6"/>
     </row>
     <row r="45" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CX45" s="6"/>
       <c r="CY45" s="6"/>
       <c r="CZ45" s="6"/>
       <c r="DA45" s="6"/>
       <c r="DB45" s="6"/>
+      <c r="DC45" s="6"/>
     </row>
     <row r="46" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT46" s="8"/>
@@ -7506,6 +7539,7 @@
       <c r="CZ46" s="6"/>
       <c r="DA46" s="6"/>
       <c r="DB46" s="6"/>
+      <c r="DC46" s="6"/>
     </row>
     <row r="47" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
@@ -7519,10 +7553,11 @@
       <c r="CZ47" s="6"/>
       <c r="DA47" s="6"/>
       <c r="DB47" s="6"/>
+      <c r="DC47" s="6"/>
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="CT48" s="8"/>
       <c r="CU48" s="8"/>
@@ -7532,6 +7567,7 @@
       <c r="CZ48" s="6"/>
       <c r="DA48" s="6"/>
       <c r="DB48" s="6"/>
+      <c r="DC48" s="6"/>
     </row>
     <row r="49" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
@@ -7542,13 +7578,14 @@
       <c r="CZ49" s="6"/>
       <c r="DA49" s="6"/>
       <c r="DB49" s="6"/>
+      <c r="DC49" s="6"/>
     </row>
     <row r="50" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX50" s="6"/>
       <c r="CY50" s="6"/>
       <c r="CZ50" s="6"/>
       <c r="DA50" s="6"/>
       <c r="DB50" s="6"/>
+      <c r="DC50" s="6"/>
     </row>
     <row r="51" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="16"/>
@@ -7703,12 +7740,13 @@
       <c r="CV51" s="18"/>
       <c r="CW51" s="18"/>
       <c r="CX51" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="CY51" s="21"/>
+        <v>53</v>
+      </c>
+      <c r="CY51" s="18"/>
       <c r="CZ51" s="21"/>
       <c r="DA51" s="21"/>
       <c r="DB51" s="21"/>
+      <c r="DC51" s="21"/>
     </row>
     <row r="52" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
@@ -8017,17 +8055,20 @@
       <c r="CX52" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="CY52" s="22"/>
+      <c r="CY52" s="7" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ52" s="22"/>
       <c r="DA52" s="22"/>
       <c r="DB52" s="22"/>
+      <c r="DC52" s="22"/>
     </row>
     <row r="53" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8"/>
-      <c r="CY53" s="6"/>
       <c r="CZ53" s="6"/>
       <c r="DA53" s="6"/>
       <c r="DB53" s="6"/>
+      <c r="DC53" s="6"/>
     </row>
     <row r="54" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
@@ -8334,13 +8375,15 @@
         <v>6.7727903869671593</v>
       </c>
       <c r="CX54" s="15">
-        <v>6.203607417561031</v>
-      </c>
-      <c r="CY54" s="17"/>
+        <v>5.8320815896901053</v>
+      </c>
+      <c r="CY54" s="15">
+        <v>9.980029490283556</v>
+      </c>
       <c r="CZ54" s="17"/>
       <c r="DA54" s="17"/>
       <c r="DB54" s="17"/>
-      <c r="DC54" s="10"/>
+      <c r="DC54" s="17"/>
       <c r="DD54" s="10"/>
       <c r="DE54" s="10"/>
       <c r="DF54" s="10"/>
@@ -8715,13 +8758,15 @@
         <v>3.983815008488051</v>
       </c>
       <c r="CX55" s="15">
-        <v>5.2640573977278393</v>
-      </c>
-      <c r="CY55" s="17"/>
+        <v>6.5271571383964613</v>
+      </c>
+      <c r="CY55" s="15">
+        <v>9.9855438298248629</v>
+      </c>
       <c r="CZ55" s="17"/>
       <c r="DA55" s="17"/>
       <c r="DB55" s="17"/>
-      <c r="DC55" s="10"/>
+      <c r="DC55" s="17"/>
       <c r="DD55" s="10"/>
       <c r="DE55" s="10"/>
       <c r="DF55" s="10"/>
@@ -9096,13 +9141,15 @@
         <v>13.962318640676969</v>
       </c>
       <c r="CX56" s="15">
-        <v>10.036654773695645</v>
-      </c>
-      <c r="CY56" s="17"/>
+        <v>8.6230802578982804</v>
+      </c>
+      <c r="CY56" s="15">
+        <v>14.590312949282776</v>
+      </c>
       <c r="CZ56" s="17"/>
       <c r="DA56" s="17"/>
       <c r="DB56" s="17"/>
-      <c r="DC56" s="10"/>
+      <c r="DC56" s="17"/>
       <c r="DD56" s="10"/>
       <c r="DE56" s="10"/>
       <c r="DF56" s="10"/>
@@ -9477,13 +9524,15 @@
         <v>15.738482232373002</v>
       </c>
       <c r="CX57" s="15">
-        <v>8.0073215312359736</v>
-      </c>
-      <c r="CY57" s="17"/>
+        <v>11.438824438418507</v>
+      </c>
+      <c r="CY57" s="15">
+        <v>7.1551739397034169</v>
+      </c>
       <c r="CZ57" s="17"/>
       <c r="DA57" s="17"/>
       <c r="DB57" s="17"/>
-      <c r="DC57" s="10"/>
+      <c r="DC57" s="17"/>
       <c r="DD57" s="10"/>
       <c r="DE57" s="10"/>
       <c r="DF57" s="10"/>
@@ -9655,11 +9704,11 @@
       <c r="CV58" s="10"/>
       <c r="CW58" s="10"/>
       <c r="CX58" s="10"/>
-      <c r="CY58" s="9"/>
+      <c r="CY58" s="10"/>
       <c r="CZ58" s="9"/>
       <c r="DA58" s="9"/>
       <c r="DB58" s="9"/>
-      <c r="DC58" s="10"/>
+      <c r="DC58" s="9"/>
       <c r="DD58" s="10"/>
       <c r="DE58" s="10"/>
       <c r="DF58" s="10"/>
@@ -10034,13 +10083,15 @@
         <v>7.3043740047124004</v>
       </c>
       <c r="CX59" s="15">
-        <v>6.5168981182013539</v>
-      </c>
-      <c r="CY59" s="17"/>
+        <v>6.5930180132913989</v>
+      </c>
+      <c r="CY59" s="15">
+        <v>10.326210552977798</v>
+      </c>
       <c r="CZ59" s="17"/>
       <c r="DA59" s="17"/>
       <c r="DB59" s="17"/>
-      <c r="DC59" s="10"/>
+      <c r="DC59" s="17"/>
       <c r="DD59" s="10"/>
       <c r="DE59" s="10"/>
       <c r="DF59" s="10"/>
@@ -10213,19 +10264,20 @@
       <c r="CV60" s="12"/>
       <c r="CW60" s="12"/>
       <c r="CX60" s="12"/>
-      <c r="CY60" s="23"/>
+      <c r="CY60" s="12"/>
       <c r="CZ60" s="23"/>
       <c r="DA60" s="23"/>
       <c r="DB60" s="23"/>
+      <c r="DC60" s="23"/>
     </row>
     <row r="61" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A61" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CY61" s="6"/>
       <c r="CZ61" s="6"/>
       <c r="DA61" s="6"/>
       <c r="DB61" s="6"/>
+      <c r="DC61" s="6"/>
     </row>
     <row r="62" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="10"/>
@@ -10329,11 +10381,11 @@
       <c r="CV62" s="10"/>
       <c r="CW62" s="10"/>
       <c r="CX62" s="10"/>
-      <c r="CY62" s="9"/>
+      <c r="CY62" s="10"/>
       <c r="CZ62" s="9"/>
       <c r="DA62" s="9"/>
       <c r="DB62" s="9"/>
-      <c r="DC62" s="10"/>
+      <c r="DC62" s="9"/>
       <c r="DD62" s="10"/>
       <c r="DE62" s="10"/>
       <c r="DF62" s="10"/>
@@ -10505,11 +10557,11 @@
       <c r="CV63" s="10"/>
       <c r="CW63" s="10"/>
       <c r="CX63" s="10"/>
-      <c r="CY63" s="9"/>
+      <c r="CY63" s="10"/>
       <c r="CZ63" s="9"/>
       <c r="DA63" s="9"/>
       <c r="DB63" s="9"/>
-      <c r="DC63" s="10"/>
+      <c r="DC63" s="9"/>
       <c r="DD63" s="10"/>
       <c r="DE63" s="10"/>
       <c r="DF63" s="10"/>
@@ -10583,67 +10635,67 @@
       <c r="A64" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="CY64" s="6"/>
       <c r="CZ64" s="6"/>
       <c r="DA64" s="6"/>
       <c r="DB64" s="6"/>
+      <c r="DC64" s="6"/>
     </row>
     <row r="65" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="CY65" s="6"/>
       <c r="CZ65" s="6"/>
       <c r="DA65" s="6"/>
       <c r="DB65" s="6"/>
+      <c r="DC65" s="6"/>
     </row>
     <row r="66" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="CY66" s="6"/>
+        <v>54</v>
+      </c>
       <c r="CZ66" s="6"/>
       <c r="DA66" s="6"/>
       <c r="DB66" s="6"/>
+      <c r="DC66" s="6"/>
     </row>
     <row r="67" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY67" s="6"/>
       <c r="CZ67" s="6"/>
       <c r="DA67" s="6"/>
       <c r="DB67" s="6"/>
+      <c r="DC67" s="6"/>
     </row>
     <row r="68" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="CY68" s="6"/>
       <c r="CZ68" s="6"/>
       <c r="DA68" s="6"/>
       <c r="DB68" s="6"/>
+      <c r="DC68" s="6"/>
     </row>
     <row r="69" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="CY69" s="6"/>
+        <v>55</v>
+      </c>
       <c r="CZ69" s="6"/>
       <c r="DA69" s="6"/>
       <c r="DB69" s="6"/>
+      <c r="DC69" s="6"/>
     </row>
     <row r="70" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="CY70" s="6"/>
       <c r="CZ70" s="6"/>
       <c r="DA70" s="6"/>
       <c r="DB70" s="6"/>
+      <c r="DC70" s="6"/>
     </row>
     <row r="71" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY71" s="6"/>
       <c r="CZ71" s="6"/>
       <c r="DA71" s="6"/>
       <c r="DB71" s="6"/>
+      <c r="DC71" s="6"/>
     </row>
     <row r="72" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="16"/>
@@ -10798,12 +10850,13 @@
       <c r="CV72" s="18"/>
       <c r="CW72" s="18"/>
       <c r="CX72" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="CY72" s="21"/>
+        <v>53</v>
+      </c>
+      <c r="CY72" s="18"/>
       <c r="CZ72" s="21"/>
       <c r="DA72" s="21"/>
       <c r="DB72" s="21"/>
+      <c r="DC72" s="21"/>
     </row>
     <row r="73" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -11112,17 +11165,20 @@
       <c r="CX73" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="CY73" s="22"/>
+      <c r="CY73" s="7" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ73" s="22"/>
       <c r="DA73" s="22"/>
       <c r="DB73" s="22"/>
+      <c r="DC73" s="22"/>
     </row>
     <row r="74" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="8"/>
-      <c r="CY74" s="6"/>
       <c r="CZ74" s="6"/>
       <c r="DA74" s="6"/>
       <c r="DB74" s="6"/>
+      <c r="DC74" s="6"/>
     </row>
     <row r="75" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
@@ -11429,13 +11485,15 @@
         <v>5.0568751723798471</v>
       </c>
       <c r="CX75" s="15">
-        <v>3.1622792379500027</v>
-      </c>
-      <c r="CY75" s="17"/>
+        <v>2.8013927094139461</v>
+      </c>
+      <c r="CY75" s="15">
+        <v>2.9864804228053572</v>
+      </c>
       <c r="CZ75" s="17"/>
       <c r="DA75" s="17"/>
       <c r="DB75" s="17"/>
-      <c r="DC75" s="10"/>
+      <c r="DC75" s="17"/>
       <c r="DD75" s="10"/>
       <c r="DE75" s="10"/>
       <c r="DF75" s="10"/>
@@ -11810,13 +11868,15 @@
         <v>2.3278363036063752</v>
       </c>
       <c r="CX76" s="15">
-        <v>2.2390819750675632</v>
-      </c>
-      <c r="CY76" s="17"/>
+        <v>3.4659297771360968</v>
+      </c>
+      <c r="CY76" s="15">
+        <v>2.9829045224829258</v>
+      </c>
       <c r="CZ76" s="17"/>
       <c r="DA76" s="17"/>
       <c r="DB76" s="17"/>
-      <c r="DC76" s="10"/>
+      <c r="DC76" s="17"/>
       <c r="DD76" s="10"/>
       <c r="DE76" s="10"/>
       <c r="DF76" s="10"/>
@@ -12191,13 +12251,15 @@
         <v>12.156264138439894</v>
       </c>
       <c r="CX77" s="15">
-        <v>6.8315767330937831</v>
-      </c>
-      <c r="CY77" s="17"/>
+        <v>5.4591759211740793</v>
+      </c>
+      <c r="CY77" s="15">
+        <v>7.2977499056147792</v>
+      </c>
       <c r="CZ77" s="17"/>
       <c r="DA77" s="17"/>
       <c r="DB77" s="17"/>
-      <c r="DC77" s="10"/>
+      <c r="DC77" s="17"/>
       <c r="DD77" s="10"/>
       <c r="DE77" s="10"/>
       <c r="DF77" s="10"/>
@@ -12572,13 +12634,15 @@
         <v>13.984267334446329</v>
       </c>
       <c r="CX78" s="15">
-        <v>4.6126009133125763</v>
-      </c>
-      <c r="CY78" s="17"/>
+        <v>7.9343371572434052</v>
+      </c>
+      <c r="CY78" s="15">
+        <v>0.35500903067904233</v>
+      </c>
       <c r="CZ78" s="17"/>
       <c r="DA78" s="17"/>
       <c r="DB78" s="17"/>
-      <c r="DC78" s="10"/>
+      <c r="DC78" s="17"/>
       <c r="DD78" s="10"/>
       <c r="DE78" s="10"/>
       <c r="DF78" s="10"/>
@@ -12750,11 +12814,11 @@
       <c r="CV79" s="10"/>
       <c r="CW79" s="10"/>
       <c r="CX79" s="10"/>
-      <c r="CY79" s="9"/>
+      <c r="CY79" s="10"/>
       <c r="CZ79" s="9"/>
       <c r="DA79" s="9"/>
       <c r="DB79" s="9"/>
-      <c r="DC79" s="10"/>
+      <c r="DC79" s="9"/>
       <c r="DD79" s="10"/>
       <c r="DE79" s="10"/>
       <c r="DF79" s="10"/>
@@ -13129,13 +13193,15 @@
         <v>5.5997727947111144</v>
       </c>
       <c r="CX80" s="15">
-        <v>3.4337673505317809</v>
-      </c>
-      <c r="CY80" s="17"/>
+        <v>3.512714525464574</v>
+      </c>
+      <c r="CY80" s="15">
+        <v>3.3268065475403432</v>
+      </c>
       <c r="CZ80" s="17"/>
       <c r="DA80" s="17"/>
       <c r="DB80" s="17"/>
-      <c r="DC80" s="10"/>
+      <c r="DC80" s="17"/>
       <c r="DD80" s="10"/>
       <c r="DE80" s="10"/>
       <c r="DF80" s="10"/>
@@ -13308,19 +13374,20 @@
       <c r="CV81" s="12"/>
       <c r="CW81" s="12"/>
       <c r="CX81" s="12"/>
-      <c r="CY81" s="23"/>
+      <c r="CY81" s="12"/>
       <c r="CZ81" s="23"/>
       <c r="DA81" s="23"/>
       <c r="DB81" s="23"/>
+      <c r="DC81" s="23"/>
     </row>
     <row r="82" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A82" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CY82" s="6"/>
       <c r="CZ82" s="6"/>
       <c r="DA82" s="6"/>
       <c r="DB82" s="6"/>
+      <c r="DC82" s="6"/>
     </row>
     <row r="83" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" s="10"/>
@@ -13423,12 +13490,12 @@
       <c r="CU83" s="10"/>
       <c r="CV83" s="10"/>
       <c r="CW83" s="10"/>
-      <c r="CX83" s="9"/>
-      <c r="CY83" s="9"/>
+      <c r="CX83" s="10"/>
+      <c r="CY83" s="10"/>
       <c r="CZ83" s="9"/>
       <c r="DA83" s="9"/>
       <c r="DB83" s="9"/>
-      <c r="DC83" s="10"/>
+      <c r="DC83" s="9"/>
       <c r="DD83" s="10"/>
       <c r="DE83" s="10"/>
       <c r="DF83" s="10"/>
@@ -13604,7 +13671,7 @@
       <c r="CZ84" s="9"/>
       <c r="DA84" s="9"/>
       <c r="DB84" s="9"/>
-      <c r="DC84" s="10"/>
+      <c r="DC84" s="9"/>
       <c r="DD84" s="10"/>
       <c r="DE84" s="10"/>
       <c r="DF84" s="10"/>
@@ -13683,16 +13750,18 @@
       <c r="CZ85" s="6"/>
       <c r="DA85" s="6"/>
       <c r="DB85" s="6"/>
+      <c r="DC85" s="6"/>
     </row>
     <row r="86" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CX86" s="6"/>
       <c r="CY86" s="6"/>
       <c r="CZ86" s="6"/>
       <c r="DA86" s="6"/>
       <c r="DB86" s="6"/>
+      <c r="DC86" s="6"/>
     </row>
     <row r="87" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CX87" s="6"/>
@@ -13700,6 +13769,7 @@
       <c r="CZ87" s="6"/>
       <c r="DA87" s="6"/>
       <c r="DB87" s="6"/>
+      <c r="DC87" s="6"/>
     </row>
     <row r="88" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
@@ -13710,16 +13780,18 @@
       <c r="CZ88" s="6"/>
       <c r="DA88" s="6"/>
       <c r="DB88" s="6"/>
+      <c r="DC88" s="6"/>
     </row>
     <row r="89" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="CX89" s="6"/>
       <c r="CY89" s="6"/>
       <c r="CZ89" s="6"/>
       <c r="DA89" s="6"/>
       <c r="DB89" s="6"/>
+      <c r="DC89" s="6"/>
     </row>
     <row r="90" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
@@ -13730,6 +13802,7 @@
       <c r="CZ90" s="6"/>
       <c r="DA90" s="6"/>
       <c r="DB90" s="6"/>
+      <c r="DC90" s="6"/>
     </row>
     <row r="92" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="16"/>
@@ -13892,6 +13965,7 @@
       <c r="DB92" s="18">
         <v>2026</v>
       </c>
+      <c r="DC92" s="18"/>
     </row>
     <row r="93" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A93" s="7" t="s">
@@ -14211,6 +14285,9 @@
       </c>
       <c r="DB93" s="14" t="s">
         <v>2</v>
+      </c>
+      <c r="DC93" s="14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -14535,7 +14612,9 @@
       <c r="DB95" s="15">
         <v>129.73110736340934</v>
       </c>
-      <c r="DC95" s="10"/>
+      <c r="DC95" s="15">
+        <v>135.15007575994687</v>
+      </c>
       <c r="DD95" s="10"/>
       <c r="DE95" s="10"/>
       <c r="DF95" s="10"/>
@@ -14926,9 +15005,11 @@
         <v>124.48218268872679</v>
       </c>
       <c r="DB96" s="15">
-        <v>128.12316166296154</v>
-      </c>
-      <c r="DC96" s="10"/>
+        <v>128.12310496668579</v>
+      </c>
+      <c r="DC96" s="15">
+        <v>133.33039365367432</v>
+      </c>
       <c r="DD96" s="10"/>
       <c r="DE96" s="10"/>
       <c r="DF96" s="10"/>
@@ -15321,7 +15402,9 @@
       <c r="DB97" s="15">
         <v>131.69406142683974</v>
       </c>
-      <c r="DC97" s="10"/>
+      <c r="DC97" s="15">
+        <v>130.12723720593215</v>
+      </c>
       <c r="DD97" s="10"/>
       <c r="DE97" s="10"/>
       <c r="DF97" s="10"/>
@@ -15712,9 +15795,11 @@
         <v>126.18899456662027</v>
       </c>
       <c r="DB98" s="15">
-        <v>130.37100228768702</v>
-      </c>
-      <c r="DC98" s="10"/>
+        <v>130.37331285551542</v>
+      </c>
+      <c r="DC98" s="15">
+        <v>137.44461053497932</v>
+      </c>
       <c r="DD98" s="10"/>
       <c r="DE98" s="10"/>
       <c r="DF98" s="10"/>
@@ -16285,9 +16370,11 @@
         <v>124.87885012824573</v>
       </c>
       <c r="DB100" s="15">
-        <v>129.61795589694938</v>
-      </c>
-      <c r="DC100" s="10"/>
+        <v>129.61165665002574</v>
+      </c>
+      <c r="DC100" s="15">
+        <v>134.05712544191169</v>
+      </c>
       <c r="DD100" s="10"/>
       <c r="DE100" s="10"/>
       <c r="DF100" s="10"/>
@@ -16468,6 +16555,7 @@
       <c r="CZ101" s="12"/>
       <c r="DA101" s="12"/>
       <c r="DB101" s="12"/>
+      <c r="DC101" s="12"/>
     </row>
     <row r="102" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A102" s="13" t="s">
@@ -16486,7 +16574,7 @@
     </row>
     <row r="107" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="109" spans="1:179" x14ac:dyDescent="0.2">
@@ -16496,7 +16584,7 @@
     </row>
     <row r="110" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="111" spans="1:179" x14ac:dyDescent="0.2">
@@ -16665,6 +16753,7 @@
       <c r="DB113" s="18">
         <v>2026</v>
       </c>
+      <c r="DC113" s="18"/>
     </row>
     <row r="114" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A114" s="7" t="s">
@@ -16984,6 +17073,9 @@
       </c>
       <c r="DB114" s="14" t="s">
         <v>2</v>
+      </c>
+      <c r="DC114" s="14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -17306,9 +17398,11 @@
         <v>48.201573748024742</v>
       </c>
       <c r="DB116" s="15">
-        <v>59.902945929972539</v>
-      </c>
-      <c r="DC116" s="10"/>
+        <v>59.650762910331586</v>
+      </c>
+      <c r="DC116" s="15">
+        <v>48.171369665754959</v>
+      </c>
       <c r="DD116" s="10"/>
       <c r="DE116" s="10"/>
       <c r="DF116" s="10"/>
@@ -17699,9 +17793,11 @@
         <v>31.826165375360866</v>
       </c>
       <c r="DB117" s="15">
-        <v>23.14367007411078</v>
-      </c>
-      <c r="DC117" s="10"/>
+        <v>23.404653349044587</v>
+      </c>
+      <c r="DC117" s="15">
+        <v>33.944814834805257</v>
+      </c>
       <c r="DD117" s="10"/>
       <c r="DE117" s="10"/>
       <c r="DF117" s="10"/>
@@ -18092,9 +18188,11 @@
         <v>13.780424475138805</v>
       </c>
       <c r="DB118" s="15">
-        <v>11.997949217758906</v>
-      </c>
-      <c r="DC118" s="10"/>
+        <v>11.835360929509703</v>
+      </c>
+      <c r="DC118" s="15">
+        <v>11.76568032384607</v>
+      </c>
       <c r="DD118" s="10"/>
       <c r="DE118" s="10"/>
       <c r="DF118" s="10"/>
@@ -18485,9 +18583,11 @@
         <v>6.1918364014755758</v>
       </c>
       <c r="DB119" s="15">
-        <v>4.9554347781577865</v>
-      </c>
-      <c r="DC119" s="10"/>
+        <v>5.1092228111141234</v>
+      </c>
+      <c r="DC119" s="15">
+        <v>6.1181351755937143</v>
+      </c>
       <c r="DD119" s="10"/>
       <c r="DE119" s="10"/>
       <c r="DF119" s="10"/>
@@ -18667,7 +18767,7 @@
       <c r="CZ120" s="15"/>
       <c r="DA120" s="15"/>
       <c r="DB120" s="15"/>
-      <c r="DC120" s="10"/>
+      <c r="DC120" s="15"/>
       <c r="DD120" s="10"/>
       <c r="DE120" s="10"/>
       <c r="DF120" s="10"/>
@@ -19060,7 +19160,9 @@
       <c r="DB121" s="15">
         <v>100</v>
       </c>
-      <c r="DC121" s="10"/>
+      <c r="DC121" s="15">
+        <v>100</v>
+      </c>
       <c r="DD121" s="10"/>
       <c r="DE121" s="10"/>
       <c r="DF121" s="10"/>
@@ -19241,6 +19343,7 @@
       <c r="CZ122" s="12"/>
       <c r="DA122" s="12"/>
       <c r="DB122" s="12"/>
+      <c r="DC122" s="12"/>
     </row>
     <row r="123" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A123" s="13" t="s">
@@ -19619,7 +19722,7 @@
     </row>
     <row r="128" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="130" spans="1:179" x14ac:dyDescent="0.2">
@@ -19629,7 +19732,7 @@
     </row>
     <row r="131" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="132" spans="1:179" x14ac:dyDescent="0.2">
@@ -19798,6 +19901,7 @@
       <c r="DB134" s="18">
         <v>2026</v>
       </c>
+      <c r="DC134" s="18"/>
     </row>
     <row r="135" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A135" s="7" t="s">
@@ -20117,6 +20221,9 @@
       </c>
       <c r="DB135" s="14" t="s">
         <v>2</v>
+      </c>
+      <c r="DC135" s="14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -20439,9 +20546,11 @@
         <v>47.952788670899018</v>
       </c>
       <c r="DB137" s="15">
-        <v>59.850698583017724</v>
-      </c>
-      <c r="DC137" s="10"/>
+        <v>59.59583910425048</v>
+      </c>
+      <c r="DC137" s="15">
+        <v>47.781810773535824</v>
+      </c>
       <c r="DD137" s="10"/>
       <c r="DE137" s="10"/>
       <c r="DF137" s="10"/>
@@ -20832,9 +20941,11 @@
         <v>31.927580720565075</v>
       </c>
       <c r="DB138" s="15">
-        <v>23.413683896210351</v>
-      </c>
-      <c r="DC138" s="10"/>
+        <v>23.676571799270771</v>
+      </c>
+      <c r="DC138" s="15">
+        <v>34.129834733946645</v>
+      </c>
       <c r="DD138" s="10"/>
       <c r="DE138" s="10"/>
       <c r="DF138" s="10"/>
@@ -21225,9 +21336,11 @@
         <v>13.992080320540975</v>
       </c>
       <c r="DB139" s="15">
-        <v>11.808806226431457</v>
-      </c>
-      <c r="DC139" s="10"/>
+        <v>11.648214965083509</v>
+      </c>
+      <c r="DC139" s="15">
+        <v>12.12100799917207</v>
+      </c>
       <c r="DD139" s="10"/>
       <c r="DE139" s="10"/>
       <c r="DF139" s="10"/>
@@ -21618,9 +21731,11 @@
         <v>6.1275502879949313</v>
       </c>
       <c r="DB140" s="15">
-        <v>4.9268112943404798</v>
-      </c>
-      <c r="DC140" s="10"/>
+        <v>5.0793741313952374</v>
+      </c>
+      <c r="DC140" s="15">
+        <v>5.9673464933454436</v>
+      </c>
       <c r="DD140" s="10"/>
       <c r="DE140" s="10"/>
       <c r="DF140" s="10"/>
@@ -22193,7 +22308,9 @@
       <c r="DB142" s="15">
         <v>100</v>
       </c>
-      <c r="DC142" s="10"/>
+      <c r="DC142" s="15">
+        <v>100</v>
+      </c>
       <c r="DD142" s="10"/>
       <c r="DE142" s="10"/>
       <c r="DF142" s="10"/>
@@ -22374,60 +22491,35 @@
       <c r="CZ143" s="12"/>
       <c r="DA143" s="12"/>
       <c r="DB143" s="12"/>
+      <c r="DC143" s="12"/>
     </row>
     <row r="144" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A144" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="98:106" x14ac:dyDescent="0.2">
-      <c r="CZ146" s="8"/>
-      <c r="DA146" s="8"/>
-      <c r="DB146" s="8"/>
+    <row r="147" spans="98:100" x14ac:dyDescent="0.2">
+      <c r="CV147" s="8"/>
     </row>
-    <row r="147" spans="98:106" x14ac:dyDescent="0.2">
-      <c r="CV147" s="8"/>
-      <c r="CZ147" s="8"/>
-      <c r="DA147" s="8"/>
-      <c r="DB147" s="8"/>
-    </row>
-    <row r="148" spans="98:106" x14ac:dyDescent="0.2">
+    <row r="148" spans="98:100" x14ac:dyDescent="0.2">
       <c r="CT148" s="8"/>
       <c r="CU148" s="8"/>
       <c r="CV148" s="8"/>
-      <c r="CX148" s="8"/>
-      <c r="CY148" s="8"/>
-      <c r="CZ148" s="8"/>
-      <c r="DA148" s="8"/>
-      <c r="DB148" s="8"/>
     </row>
-    <row r="149" spans="98:106" x14ac:dyDescent="0.2">
+    <row r="149" spans="98:100" x14ac:dyDescent="0.2">
       <c r="CT149" s="8"/>
       <c r="CU149" s="8"/>
       <c r="CV149" s="8"/>
-      <c r="CX149" s="8"/>
-      <c r="CY149" s="8"/>
-      <c r="CZ149" s="8"/>
-      <c r="DA149" s="8"/>
-      <c r="DB149" s="8"/>
     </row>
-    <row r="150" spans="98:106" x14ac:dyDescent="0.2">
+    <row r="150" spans="98:100" x14ac:dyDescent="0.2">
       <c r="CT150" s="8"/>
       <c r="CU150" s="8"/>
       <c r="CV150" s="8"/>
-      <c r="CX150" s="8"/>
-      <c r="CY150" s="8"/>
-      <c r="CZ150" s="8"/>
-      <c r="DA150" s="8"/>
     </row>
-    <row r="151" spans="98:106" x14ac:dyDescent="0.2">
+    <row r="151" spans="98:100" x14ac:dyDescent="0.2">
       <c r="CT151" s="8"/>
       <c r="CU151" s="8"/>
       <c r="CV151" s="8"/>
-      <c r="CX151" s="8"/>
-      <c r="CY151" s="8"/>
-      <c r="CZ151" s="8"/>
-      <c r="DA151" s="8"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -22435,9 +22527,9 @@
   <pageSetup paperSize="9" scale="31" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="42" max="105" man="1"/>
-    <brk id="84" max="105" man="1"/>
-    <brk id="104" max="105" man="1"/>
+    <brk id="42" max="106" man="1"/>
+    <brk id="84" max="106" man="1"/>
+    <brk id="104" max="106" man="1"/>
   </rowBreaks>
   <colBreaks count="2" manualBreakCount="2">
     <brk id="29" max="144" man="1"/>
